--- a/tame_output/ON/bt/strategyON_20240927.xlsx
+++ b/tame_output/ON/bt/strategyON_20240927.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.8%</t>
+          <t>-575.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-51.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.3%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.2%</t>
+          <t>-319.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767451</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225436</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226416</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472732</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798533</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705321</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982222</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760807</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131244</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206786</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181163</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394723</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852419</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319538</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799958</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331111</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077635</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.032250168264161</v>
+        <v>-4.071763611188066</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.229137367760532</v>
+        <v>2.21333199059097</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.198843393377683</v>
+        <v>-4.238356836301588</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.131903029069206</v>
+        <v>2.116097651899644</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.175807600016118</v>
+        <v>-4.215321042940023</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.14479374907555</v>
+        <v>2.128988371905988</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.146561619560421</v>
+        <v>-4.186075062484326</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.154110196381324</v>
+        <v>2.138304819211762</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.253487167438272</v>
+        <v>-4.293000610362177</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.108633216387819</v>
+        <v>2.092827839218256</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.398505725945521</v>
+        <v>-4.438019168869426</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.052054595128153</v>
+        <v>2.036249217958591</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.516847491730238</v>
+        <v>-4.556360934654143</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.104649128072019</v>
+        <v>2.088843750902457</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.568257914050946</v>
+        <v>-4.607771356974851</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.081870656269675</v>
+        <v>2.066065279100113</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437327</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.647677365258698</v>
+        <v>-4.687190808182603</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.050006003860864</v>
+        <v>2.034200626691302</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.743140363175915</v>
+        <v>-4.78265380609982</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.01181469825202</v>
+        <v>1.996009321082457</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.678764452325201</v>
+        <v>-4.718277895249106</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.035661459154916</v>
+        <v>2.019856081985354</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.734133614457394</v>
+        <v>-4.773647057381299</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.019247612049766</v>
+        <v>2.003442234880203</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.752352081455003</v>
+        <v>-4.791865524378908</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.011498588593655</v>
+        <v>1.995693211424092</v>
       </c>
       <c r="F2064" t="n">
         <v>1.221063841660525</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.664145247307425</v>
+        <v>-4.70365869023133</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.066655715103004</v>
+        <v>2.050850337933442</v>
       </c>
       <c r="F2065" t="n">
         <v>1.221063841660525</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.558110252102115</v>
+        <v>-4.59762369502602</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.092770413709856</v>
+        <v>2.076965036540294</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.37489858896902</v>
+        <v>-4.414412031892925</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.168486028427139</v>
+        <v>2.152680651257577</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.303177141955169</v>
+        <v>-4.342690584879074</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180119013312057</v>
+        <v>2.164313636142495</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
@@ -49132,16 +49132,16 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.280804116347463</v>
+        <v>-4.320317559271368</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.135983969476311</v>
+        <v>2.120178592306749</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.313820412258208</v>
+        <v>-4.353333855182113</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.307975655997369</v>
+        <v>2.292170278827807</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.302292776608599</v>
+        <v>-4.341806219532504</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304507936085462</v>
+        <v>2.288702558915899</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
@@ -49201,16 +49201,16 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.399634277950968</v>
+        <v>-4.439147720874873</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269239448070302</v>
+        <v>2.25343407090074</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
@@ -49224,16 +49224,16 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.485490307290934</v>
+        <v>-4.525003750214839</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236148118527154</v>
+        <v>2.220342741357592</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
@@ -49247,16 +49247,16 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.494327104707054</v>
+        <v>-4.533840547630959</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.215032601381208</v>
+        <v>2.199227224211646</v>
       </c>
       <c r="F2074" t="n">
         <v>1.199365897288914</v>
@@ -49270,16 +49270,16 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.585709667272512</v>
+        <v>-4.625223110196417</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.188644087400074</v>
+        <v>2.172838710230512</v>
       </c>
       <c r="F2075" t="n">
         <v>1.162801012569569</v>
@@ -49293,16 +49293,16 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.574002949285506</v>
+        <v>-4.613516392209411</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.295455032419145</v>
+        <v>2.279649655249583</v>
       </c>
       <c r="F2076" t="n">
         <v>1.174507730556575</v>
@@ -49316,16 +49316,16 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.644915023027784</v>
+        <v>-4.684428465951688</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.270122541653638</v>
+        <v>2.254317164484076</v>
       </c>
       <c r="F2077" t="n">
         <v>1.174507730556575</v>
@@ -49339,16 +49339,16 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.655231121194136</v>
+        <v>-4.69474456411804</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.478900935665155</v>
+        <v>2.463095558495594</v>
       </c>
       <c r="F2078" t="n">
         <v>1.174507730556575</v>
@@ -49362,16 +49362,16 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.655137153176764</v>
+        <v>-4.694650596100668</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.478117189784195</v>
+        <v>2.462311812614632</v>
       </c>
       <c r="F2079" t="n">
         <v>1.174877591903893</v>
@@ -49385,16 +49385,16 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.803503380832908</v>
+        <v>-4.843016823756813</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.413002684666091</v>
+        <v>2.397197307496528</v>
       </c>
       <c r="F2080" t="n">
         <v>1.174877591903893</v>
@@ -49408,16 +49408,16 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.80255495771487</v>
+        <v>-4.842068400638774</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.413382053913306</v>
+        <v>2.397576676743744</v>
       </c>
       <c r="F2081" t="n">
         <v>1.174877591903893</v>
@@ -49431,16 +49431,16 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.902824775673891</v>
+        <v>-4.942338218597795</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.386001734710789</v>
+        <v>2.370196357541227</v>
       </c>
       <c r="F2082" t="n">
         <v>1.174877591903893</v>
@@ -49454,16 +49454,16 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.89683252888508</v>
+        <v>-4.936345971808984</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.390344631850701</v>
+        <v>2.37453925468114</v>
       </c>
       <c r="F2083" t="n">
         <v>1.174877591903893</v>
@@ -49477,16 +49477,16 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.808274567754312</v>
+        <v>-4.847788010678216</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.419421952320778</v>
+        <v>2.403616575151216</v>
       </c>
       <c r="F2084" t="n">
         <v>1.174877591903893</v>
@@ -49500,16 +49500,16 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.790515490251238</v>
+        <v>-4.830028933175142</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.425834260761003</v>
+        <v>2.410028883591441</v>
       </c>
       <c r="F2085" t="n">
         <v>1.174877591903893</v>
@@ -49523,16 +49523,16 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.69088533920217</v>
+        <v>-4.730398782126074</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.478468507089217</v>
+        <v>2.462663129919655</v>
       </c>
       <c r="F2086" t="n">
         <v>1.274507742952961</v>
@@ -49546,16 +49546,16 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.740284847891181</v>
+        <v>-4.779798290815085</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.647862969112339</v>
+        <v>2.632057591942777</v>
       </c>
       <c r="F2087" t="n">
         <v>1.284766576384706</v>
@@ -49569,16 +49569,16 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.533600374248805</v>
+        <v>-4.573113817172709</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.717725431672151</v>
+        <v>2.701920054502589</v>
       </c>
       <c r="F2088" t="n">
         <v>1.491451050027081</v>
@@ -49592,16 +49592,16 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.567757269246331</v>
+        <v>-4.607270712170235</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.706064187327246</v>
+        <v>2.690258810157684</v>
       </c>
       <c r="F2089" t="n">
         <v>1.407867280486269</v>
@@ -49615,16 +49615,16 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.475167790184875</v>
+        <v>-4.514681233108779</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.096597092941495</v>
+        <v>3.080791715771934</v>
       </c>
       <c r="F2090" t="n">
         <v>1.407867280486269</v>
@@ -49638,16 +49638,16 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.535056418008425</v>
+        <v>-4.574569860932329</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.077204753379179</v>
+        <v>3.061399376209617</v>
       </c>
       <c r="F2091" t="n">
         <v>1.393745365798804</v>
@@ -49661,16 +49661,16 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.482840108212083</v>
+        <v>-4.522353551135987</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.147921218621243</v>
+        <v>3.132115841451681</v>
       </c>
       <c r="F2092" t="n">
         <v>1.393745365798804</v>
@@ -49684,16 +49684,16 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.450942591126838</v>
+        <v>-4.490456034050742</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.169494195665352</v>
+        <v>3.15368881849579</v>
       </c>
       <c r="F2093" t="n">
         <v>1.42564288288405</v>
@@ -49707,16 +49707,16 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.465697915326978</v>
+        <v>-4.505211358250882</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.159229650024493</v>
+        <v>3.143424272854931</v>
       </c>
       <c r="F2094" t="n">
         <v>1.42564288288405</v>
@@ -49730,16 +49730,16 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.416233291957067</v>
+        <v>-4.455746734880971</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.169940002788738</v>
+        <v>3.154134625619175</v>
       </c>
       <c r="F2095" t="n">
         <v>1.475107506253962</v>
@@ -49753,16 +49753,16 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479219</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.253125299803451</v>
+        <v>-4.292638742727355</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.231590867365118</v>
+        <v>3.215785490195556</v>
       </c>
       <c r="F2096" t="n">
         <v>1.638215498407577</v>
@@ -49776,16 +49776,16 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.120317674306285</v>
+        <v>-4.159831117230189</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.293760954255113</v>
+        <v>3.277955577085551</v>
       </c>
       <c r="F2097" t="n">
         <v>1.638215498407577</v>
@@ -49799,16 +49799,16 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.183025590780843</v>
+        <v>-4.222539033704747</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.269535252651411</v>
+        <v>3.253729875481849</v>
       </c>
       <c r="F2098" t="n">
         <v>1.575507581933019</v>
@@ -49822,16 +49822,16 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.790288108713228</v>
+        <v>3.899379203875191</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.142509346380904</v>
+        <v>-4.140683023368438</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.248651167201739</v>
+        <v>3.249381696406725</v>
       </c>
       <c r="F2099" t="n">
         <v>1.575507581933019</v>

--- a/tame_output/ON/bt/strategyON_20240927.xlsx
+++ b/tame_output/ON/bt/strategyON_20240927.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.5%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.6%</t>
+          <t>-587.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-55.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.3%</t>
+          <t>-319.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-72.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>132.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>120.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>139.1%</t>
+          <t>135.3%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783972</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.032094976812242</v>
+        <v>-4.151066053975958</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9829936193917896</v>
+        <v>0.9354051885263035</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.2618676654287915</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.791313761183068</v>
+        <v>2.75330863368771</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.012738840918395</v>
+        <v>-4.131709918082111</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9967446041462547</v>
+        <v>0.9491561732807683</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.2618676654287915</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.797322291579994</v>
+        <v>2.759317164084636</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.864995870683393</v>
+        <v>-3.983966947847108</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9537920135174549</v>
+        <v>0.9062035826519688</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.4296750226636746</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795956927198123</v>
+        <v>2.757951799702765</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.948817091958091</v>
+        <v>-4.067788169121807</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9230571465390567</v>
+        <v>0.8754687156735705</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.4296750226636746</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798750548729604</v>
+        <v>2.760745421234246</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.942664385905307</v>
+        <v>-4.061635463069022</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9261805773518288</v>
+        <v>0.8785921464863427</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4991696078753898</v>
+        <v>0.4358277287164589</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.803104520752933</v>
+        <v>2.765099393257575</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.959473684055808</v>
+        <v>-4.078444761219524</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9185373348317385</v>
+        <v>0.8709489039662521</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4823603097248881</v>
+        <v>0.4190184305659573</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.792099418602743</v>
+        <v>2.754094291107384</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.897175685279686</v>
+        <v>-4.016146762443402</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.009792088139008</v>
+        <v>0.962203657273522</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5276545739993301</v>
+        <v>0.4643126948403993</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.885611530964229</v>
+        <v>2.847606403468871</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.695385487614528</v>
+        <v>-3.814356564778244</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8928001689191984</v>
+        <v>0.8452117380537121</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7256727661684845</v>
+        <v>0.6623308870095537</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.806714447979849</v>
+        <v>2.76870932048449</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.746272200300723</v>
+        <v>-3.865243277464439</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9427357161668957</v>
+        <v>0.8951472853014095</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.67478605348229</v>
+        <v>0.6114441743233592</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846472652690307</v>
+        <v>2.808467525194949</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.659661457650916</v>
+        <v>-3.778632534814631</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9920077493428623</v>
+        <v>0.9444193184773759</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7534117846874483</v>
+        <v>0.6900699055285174</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.908275827529446</v>
+        <v>2.870270700034087</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.7198707556562</v>
+        <v>-3.838841832819916</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9664600109654202</v>
+        <v>0.9188715800999339</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.6298606075232329</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.870686229550947</v>
+        <v>2.832681102055588</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.670684106971849</v>
+        <v>-3.789655184135564</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9846262884790893</v>
+        <v>0.9370378576136029</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.6298606075232329</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.869177847590875</v>
+        <v>2.831172720095517</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.62631097533328</v>
+        <v>-3.745282052496996</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.002238408569953</v>
+        <v>0.9546499777044666</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.6742337391618015</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.895664594009453</v>
+        <v>2.857659466514094</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.591579654014779</v>
+        <v>-3.710550731178495</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.010524731235944</v>
+        <v>0.9629363003704576</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.6742337391618015</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.890058388148043</v>
+        <v>2.852053260652684</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.543923923453724</v>
+        <v>-3.662895000617439</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.035968780488171</v>
+        <v>0.9883803496226844</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.785231348881788</v>
+        <v>0.7218894697228572</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.925033583512481</v>
+        <v>2.887028456017123</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.443405764954969</v>
+        <v>-3.562376842118685</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.081068417262397</v>
+        <v>1.033479986396911</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8857495073805426</v>
+        <v>0.8224076282216117</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.990236851986459</v>
+        <v>2.9522317244911</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.427500435522616</v>
+        <v>-3.546471512686332</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.074185221511211</v>
+        <v>1.026596790645724</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8066368466713036</v>
+        <v>0.7432949675123728</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929523928036788</v>
+        <v>2.891518800541429</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.382662033914218</v>
+        <v>-3.501633111077934</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.096218284765198</v>
+        <v>1.048629853899712</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8111802796161731</v>
+        <v>0.7478384004572423</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936347690414338</v>
+        <v>2.898342562918979</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.402160490156227</v>
+        <v>-3.521131567319942</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.092579841899473</v>
+        <v>1.044991411033987</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7630956383362688</v>
+        <v>0.699753759177338</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.911657845277473</v>
+        <v>2.873652717782115</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.357957653070326</v>
+        <v>-3.476928730234042</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.11614057926167</v>
+        <v>1.068552148396184</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8072984754221693</v>
+        <v>0.7439565962632384</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.944059150056851</v>
+        <v>2.906054022561492</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.365517318907373</v>
+        <v>-3.484488396071089</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.111526713396099</v>
+        <v>1.063938282530613</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.7987600002730577</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.97535119293199</v>
+        <v>2.937346065436631</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.207225901368101</v>
+        <v>-3.326196978531816</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.226091045594848</v>
+        <v>1.178502614729362</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.7987600002730577</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.026598958115029</v>
+        <v>2.988593830619671</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.999583897733625</v>
+        <v>-3.11855497489734</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.307588551642891</v>
+        <v>1.260000120777405</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.069743883066465</v>
+        <v>1.006402003907534</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.149624864889968</v>
+        <v>3.11161973739461</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.948551805011097</v>
+        <v>-3.067522882174812</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.322949616970173</v>
+        <v>1.275361186104686</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.120775975788993</v>
+        <v>1.057434096630062</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175192348761755</v>
+        <v>3.137187221266397</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.883327623883891</v>
+        <v>-3.002298701047606</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.36622669351376</v>
+        <v>1.318638262648274</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.186000156916198</v>
+        <v>1.122658277757268</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.231514261530783</v>
+        <v>3.193509134035425</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.845900603812757</v>
+        <v>-2.964871680976473</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.377158473841494</v>
+        <v>1.329570042976008</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19125169494538</v>
+        <v>1.127909815786449</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.230626156647573</v>
+        <v>3.192621029152214</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.844542618839212</v>
+        <v>-2.963513696002927</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.378958460162152</v>
+        <v>1.331370029296666</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.265589820483199</v>
+        <v>1.202247941324268</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.276485824301504</v>
+        <v>3.238480696806146</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.816129355739328</v>
+        <v>-2.935100432903043</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.550881536423316</v>
+        <v>1.50329310555783</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.20661425773677</v>
+        <v>1.143272378577839</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.401658257674858</v>
+        <v>3.363653130179499</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.741347094714315</v>
+        <v>-2.860318171878031</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.700907350051139</v>
+        <v>1.653318919185653</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.281396518761783</v>
+        <v>1.218054639602852</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.566640523507683</v>
+        <v>3.528635396012324</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.715263010450507</v>
+        <v>-2.834234087614223</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.703048959770521</v>
+        <v>1.655460528905035</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.281396518761783</v>
+        <v>1.218054639602852</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.558348499521542</v>
+        <v>3.520343372026183</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.627385097341387</v>
+        <v>-2.746356174505102</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.736393320597948</v>
+        <v>1.688804889732462</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.397322161185134</v>
+        <v>1.333980282026203</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626097080559332</v>
+        <v>3.588091953063973</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.618492635948104</v>
+        <v>-2.737463713111819</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.757504710882053</v>
+        <v>1.709916280016567</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.397322161185134</v>
+        <v>1.333980282026203</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.643651486286123</v>
+        <v>3.605646358790764</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.786968752917982</v>
+        <v>-2.905939830081697</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.681969311498686</v>
+        <v>1.6343808806332</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.369374325468553</v>
+        <v>1.306032446309622</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.618737832260758</v>
+        <v>3.5807327047654</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.340712560288542</v>
+        <v>-2.459683637452257</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.841741485738324</v>
+        <v>1.794153054872837</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.27465565579892</v>
+        <v>1.211313776639989</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.543176327646841</v>
+        <v>3.505171200151482</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.317991456605389</v>
+        <v>-2.436962533769105</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.841493949708489</v>
+        <v>1.793905518843003</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.27465565579892</v>
+        <v>1.211313776639989</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533840350143745</v>
+        <v>3.495835222648387</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.447193269899432</v>
+        <v>-2.566164347063147</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.948719350242041</v>
+        <v>1.901130919376555</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.145453842504878</v>
+        <v>1.082111963345947</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.615225388018489</v>
+        <v>3.577220260523131</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.473067668373457</v>
+        <v>-2.592038745537173</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.975447413346078</v>
+        <v>1.927858982480592</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.190365451216619</v>
+        <v>1.127023572057688</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67925017573918</v>
+        <v>3.641245048243822</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.466012978158284</v>
+        <v>-2.584984055321999</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.974944645421692</v>
+        <v>1.927356214556206</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.197420141431793</v>
+        <v>1.134078262272862</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.642153218362471</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.439061753831796</v>
+        <v>-2.558032830995511</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.995731288797029</v>
+        <v>1.948142857931543</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.212300487459512</v>
+        <v>1.148958608300581</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.661087579623844</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.460605981662583</v>
+        <v>-2.579577058826299</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.171216729809674</v>
+        <v>2.123628298944188</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.212300487459512</v>
+        <v>1.148958608300581</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.845190711768804</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.483014099467455</v>
+        <v>-2.601985176631171</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.154370177590718</v>
+        <v>2.106781746725232</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.212300487459512</v>
+        <v>1.148958608300581</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.837307406671797</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.511238335045055</v>
+        <v>-2.630209412208771</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.145134482909316</v>
+        <v>2.097546052043829</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.230277239910821</v>
+        <v>1.16693536075189</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.850147457692219</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.520679260933585</v>
+        <v>-2.639650338097301</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.197611830275751</v>
+        <v>2.150023399410264</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.352704357454212</v>
+        <v>1.289362478295281</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>3.979857445940102</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.609555892102059</v>
+        <v>-2.728526969265775</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.164952272353662</v>
+        <v>2.117363841488176</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>1.200485847126807</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.929422561784318</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.685885869702965</v>
+        <v>-2.804856946866681</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.132532094207074</v>
+        <v>2.084943663341589</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>1.200485847126807</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.927534374678094</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.840842655103094</v>
+        <v>-2.95981373226681</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.065369609649886</v>
+        <v>2.017781178784399</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.108870940885609</v>
+        <v>1.045529061726678</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.867385660536237</v>
+        <v>3.829380533040878</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.002411080630349</v>
+        <v>-3.121382157794065</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.999176249649135</v>
+        <v>1.951587818783649</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.9187461379287988</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.789749916467661</v>
+        <v>3.751744788972303</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.110711742500469</v>
+        <v>-3.229682819664184</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.968929391767007</v>
+        <v>1.92134096090152</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.9187461379287988</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.80282332333358</v>
+        <v>3.764818195838222</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.128515714221213</v>
+        <v>-3.247486791384929</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.953812999861649</v>
+        <v>1.906224568996163</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9115533941825285</v>
+        <v>0.8482115150235976</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.714502618878041</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.156416501330686</v>
+        <v>-3.275387578494402</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.941176726144862</v>
+        <v>1.893588295279375</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8769564700395936</v>
+        <v>0.8136145908806628</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.692268505519282</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.27894260403358</v>
+        <v>-3.397913681197295</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.888930729040903</v>
+        <v>1.841342298175417</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7544303673366998</v>
+        <v>0.6910884881777689</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.615517287874744</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.509457100219168</v>
+        <v>-3.628428177382884</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.863430890157171</v>
+        <v>1.815842459291685</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.523915871151111</v>
+        <v>0.4605739919921802</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.543914549753895</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.858202185443612</v>
+        <v>-3.977173262607328</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.864244575069241</v>
+        <v>1.816656144203755</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3518260380732824</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.618977496404403</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.012188603219752</v>
+        <v>-4.131159680383468</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.871630277104424</v>
+        <v>1.824041846238938</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3518260380732824</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.687957765550043</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.216788038082761</v>
+        <v>-4.335759115246477</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.775841705279342</v>
+        <v>1.728253274413855</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3518260380732824</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.674008967670164</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.469263192090486</v>
+        <v>-4.588234269254201</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.686722132731666</v>
+        <v>1.63913370186618</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3518260380732824</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.685879456725578</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.762158948569898</v>
+        <v>-4.881130025733613</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.570774364658845</v>
+        <v>1.523185933793359</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3518260380732824</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.687089991244521</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.948823076704706</v>
+        <v>-5.067794153868421</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.500230455632243</v>
+        <v>1.452642024766757</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3884289464076534</v>
+        <v>0.3250870672487225</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.675168350977107</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.094843763618668</v>
+        <v>-5.213814840782383</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.436900033602848</v>
+        <v>1.389311602737362</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.3160039754548655</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.664796348636982</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.186557772728253</v>
+        <v>-5.305528849891969</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.562418486658057</v>
+        <v>1.514830055792571</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.3160039754548655</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.827000405336026</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.218209431788223</v>
+        <v>-5.337180508951938</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.544604460997884</v>
+        <v>1.497016030132398</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3741773973693562</v>
+        <v>0.3108355182104253</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.818745968953177</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.28727548636116</v>
+        <v>-5.406246563524875</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.5272074567372</v>
+        <v>1.479619025871714</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3118065198757461</v>
+        <v>0.2484646407168153</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.791552860025502</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.389251608609567</v>
+        <v>-5.508222685773283</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.49534264629374</v>
+        <v>1.447754215428254</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2098303976273386</v>
+        <v>0.1464885184684077</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.73929282513236</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.279245325132345</v>
+        <v>-5.398216402296061</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.531498046928804</v>
+        <v>1.483909616063317</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2330349695446138</v>
+        <v>0.1696930903856829</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.7453684555269</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.136185749391419</v>
+        <v>-5.255156826555135</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.592971887947149</v>
+        <v>1.545383457081662</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2410483961345931</v>
+        <v>0.1777065169756622</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.754426522202862</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.834739023919582</v>
+        <v>-4.953710101083297</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.72081146101842</v>
+        <v>1.673223030152933</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.4791532424474995</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>3.9425554403685</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.859329268154766</v>
+        <v>-4.978300345318481</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.711946541077057</v>
+        <v>1.66435811021157</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.4791532424474995</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>3.943526618121211</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.808290892148245</v>
+        <v>-4.927261969311961</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.73320479585942</v>
+        <v>1.685616364993934</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.4791532424474995</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>3.944369522500966</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.767151597281615</v>
+        <v>-4.88612267444533</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.768698612680218</v>
+        <v>1.721110181814732</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5836344164730611</v>
+        <v>0.5202925373141303</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>3.98809119829509</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.670516685262974</v>
+        <v>-4.78948776242669</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.623536573611609</v>
+        <v>1.575948142746122</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6802693284917011</v>
+        <v>0.6169274493327702</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.862256141630209</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.601478674314507</v>
+        <v>-4.720449751478222</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65465382206496</v>
+        <v>1.607065391199474</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7493073394401691</v>
+        <v>0.6859654602812383</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>3.907180992273254</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.436982340123545</v>
+        <v>-4.55595341728726</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.704879174817427</v>
+        <v>1.657290743951941</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.913803673631131</v>
+        <v>0.8504617944722002</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>3.990305611863914</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.359883738581672</v>
+        <v>-4.478854815745388</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.734906325870606</v>
+        <v>1.68731789500512</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.913803673631131</v>
+        <v>0.8504617944722002</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>3.989493322300343</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.370268933471562</v>
+        <v>-4.489240010635277</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.740621027039723</v>
+        <v>1.693032596174236</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9034184787412417</v>
+        <v>0.8400765995823108</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>3.993130984491482</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.388857092193787</v>
+        <v>-4.507828169357502</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.804022769327258</v>
+        <v>1.756434338461772</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8848303200190164</v>
+        <v>0.8214884408600855</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>4.052815095034572</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.389155638889823</v>
+        <v>-4.508126716053538</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.800772361467142</v>
+        <v>1.753183930601656</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8845317733229805</v>
+        <v>0.8211898941640496</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>4.049504977835249</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.288332505199395</v>
+        <v>-4.40730358236311</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.845632509882704</v>
+        <v>1.798044079017218</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8969959888073343</v>
+        <v>0.8336541096484035</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>4.061514402065253</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.097551144446987</v>
+        <v>-4.216522221610703</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.922074307662211</v>
+        <v>1.874485876796725</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.087777349559742</v>
+        <v>1.024435470400811</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.17611247199524</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.990587786597565</v>
+        <v>-4.109558863761281</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.944696496539576</v>
+        <v>1.89710806567409</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>1.082900078360612</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.191028082508717</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.935257198695803</v>
+        <v>-4.054228275859519</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.001795668312339</v>
+        <v>1.954207237446853</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.138230666262374</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.259193371861834</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.923203071782841</v>
+        <v>-4.042174148946556</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.000303886978962</v>
+        <v>1.952715456113476</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.150284793175337</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.260112415911049</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.964358191351061</v>
+        <v>-4.083329268514777</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.985722469335809</v>
+        <v>1.938134038470324</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.109129673607116</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.237299974354253</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.896309628659532</v>
+        <v>-4.015280705823247</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.025792920290304</v>
+        <v>1.978204489424818</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.177178236298646</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.290980137847052</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.127910021829033</v>
+        <v>-4.246881098992747</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.953355433196098</v>
+        <v>1.905767002330612</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.177178236298646</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.311182808020646</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.177961567358253</v>
+        <v>-4.296932644521966</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.916941051051292</v>
+        <v>1.869352620185806</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.177178236298646</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.294789044087529</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.353068399934697</v>
+        <v>-4.472039477098411</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.807150231614181</v>
+        <v>1.759561800748695</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.177178236298646</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.255040957680995</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.156968246504174</v>
+        <v>-4.275939323667888</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.89261291198333</v>
+        <v>1.845024481117844</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.373278389729169</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.379723668736249</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.003942854390891</v>
+        <v>-4.122913931554604</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.052994068401548</v>
+        <v>2.005405637536063</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.526303781842453</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.570709903577124</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.071763611188066</v>
+        <v>-4.151221245427874</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.21333199059097</v>
+        <v>2.181548936895047</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.526303781842453</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.758176128485417</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.238356836301588</v>
+        <v>-4.317814470541396</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.116097651899644</v>
+        <v>2.084314598203721</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.35971055672893</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.627623144771386</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.215321042940023</v>
+        <v>-4.29477867717983</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.128988371905988</v>
+        <v>2.097205318210065</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.35971055672893</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.631299547433104</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.186075062484326</v>
+        <v>-4.265532696724134</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.138304819211762</v>
+        <v>2.106521765515839</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.35971055672893</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.628917602556599</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.293000610362177</v>
+        <v>-4.372458244601985</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.092827839218256</v>
+        <v>2.061044785522333</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.252785008851079</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.562055512987523</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.438019168869426</v>
+        <v>-4.517476803109234</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.036249217958591</v>
+        <v>2.004466164262668</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.107766450343831</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.476473180026408</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.556360934654143</v>
+        <v>-4.635818568893951</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.088843750902457</v>
+        <v>2.057060697206534</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.118452488906721</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.582816042421896</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.607771356974851</v>
+        <v>-4.687228991214659</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.066065279100113</v>
+        <v>2.03428222540419</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.118452488906721</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.580601739547834</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.687190808182603</v>
+        <v>-4.766648442422411</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.034200626691302</v>
+        <v>2.002417572995379</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.118452488906721</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.580504867622124</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.78265380609982</v>
+        <v>-4.862111440339628</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.996009321082457</v>
+        <v>1.964226267386534</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.118452488906721</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.580498761180166</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.718277895249106</v>
+        <v>-4.797735529488913</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.019856081985354</v>
+        <v>1.988073028289431</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.182828399757436</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.617220704253207</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.773647057381299</v>
+        <v>-4.853104691621107</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.003442234880203</v>
+        <v>1.97165918118428</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.182828399757436</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.622954522000933</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.791865524378908</v>
+        <v>-4.871323158618716</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.995693211424092</v>
+        <v>1.963910157728169</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>1.157721962501594</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.60742902299036</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.70365869023133</v>
+        <v>-4.783116324471138</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.050850337933442</v>
+        <v>2.019067284237519</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>1.157721962501594</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.627303415840679</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.59762369502602</v>
+        <v>-4.677081329265828</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.076965036540294</v>
+        <v>2.045181982844371</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>1.157721962501594</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.611004116365407</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.414412031892925</v>
+        <v>-4.493869666132733</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.152680651257577</v>
+        <v>2.120897597561654</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>1.157721962501594</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.613435065829452</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.342690584879074</v>
+        <v>-4.422148219118882</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.164313636142495</v>
+        <v>2.132530582446572</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>1.229443409515445</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.677417467612498</v>
+        <v>4.63941234011714</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.320317559271368</v>
+        <v>-4.399775193511176</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.120178592306749</v>
+        <v>2.088395538610825</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>1.240699160628346</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.63108666420141</v>
+        <v>4.593081536706052</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.353333855182113</v>
+        <v>-4.432791489421921</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.292170278827807</v>
+        <v>2.260387225131884</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>1.171261783961594</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.774622443086715</v>
+        <v>4.736617315591356</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.341806219532504</v>
+        <v>-4.421263853772312</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.288702558915899</v>
+        <v>2.256919505219976</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>1.230262442162957</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.801944063835782</v>
+        <v>4.763938936340423</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.439147720874873</v>
+        <v>-4.518605355114681</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.25343407090074</v>
+        <v>2.221651017204817</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>1.185842259997469</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.778960067058277</v>
+        <v>4.740954939562918</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427684</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.525003750214839</v>
+        <v>-4.604461384454647</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.220342741357592</v>
+        <v>2.188559687661669</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>1.143466190771333</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.754785507715434</v>
+        <v>4.716780380220076</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.533840547630959</v>
+        <v>-4.613298181870767</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.199227224211646</v>
+        <v>2.167444170515723</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>1.136024018129983</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.732739405951126</v>
+        <v>4.694734278455767</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667455</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.625223110196417</v>
+        <v>-4.704680744436225</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.172838710230512</v>
+        <v>2.141055656534589</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>1.099459133410638</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.720964986164568</v>
+        <v>4.68295985866921</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889191</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.613516392209411</v>
+        <v>-4.692974026449219</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.279649655249583</v>
+        <v>2.247866601553659</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>1.111165851397645</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.83011727478104</v>
+        <v>4.792112147285682</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.684428465951688</v>
+        <v>-4.763886100191497</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.254317164484076</v>
+        <v>2.222534110788153</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.174507730556575</v>
+        <v>1.111165851397645</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.833149613512445</v>
+        <v>4.795144486017087</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.69474456411804</v>
+        <v>-4.774202198357849</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.463095558495594</v>
+        <v>2.43131250479967</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.174507730556575</v>
+        <v>1.111165851397645</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.046054446790503</v>
+        <v>5.008049319295145</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.694650596100668</v>
+        <v>-4.774108230340476</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.462311812614632</v>
+        <v>2.430528758918709</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.045455030510984</v>
+        <v>5.007449903015625</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.843016823756813</v>
+        <v>-4.922474457996621</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.397197307496528</v>
+        <v>2.365414253800605</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.039687016455337</v>
+        <v>5.001681888959979</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740923</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.842068400638774</v>
+        <v>-4.921526034878583</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.397576676743744</v>
+        <v>2.36579362304782</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.039687016455337</v>
+        <v>5.001681888959979</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.942338218597795</v>
+        <v>-5.021795852837604</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.370196357541227</v>
+        <v>2.338413303845304</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.052414624436429</v>
+        <v>5.014409496941071</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.936345971808984</v>
+        <v>-5.015803606048792</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.37453925468114</v>
+        <v>2.342756200985216</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.054360622860817</v>
+        <v>5.016355495365459</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.847788010678216</v>
+        <v>-4.927245644918025</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.403616575151216</v>
+        <v>2.371833521455292</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.048014758878586</v>
+        <v>5.010009631383228</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.830028933175142</v>
+        <v>-4.909486567414951</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.410028883591441</v>
+        <v>2.378245829895517</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.174877591903893</v>
+        <v>1.111535712744963</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.047323436317582</v>
+        <v>5.009318308822223</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720998</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.730398782126074</v>
+        <v>-4.809856416365883</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.462663129919655</v>
+        <v>2.430880076223731</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.274507742952961</v>
+        <v>1.21116586379403</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.119883712855609</v>
+        <v>5.081878585360251</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455272</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.779798290815085</v>
+        <v>-4.859255925054894</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.632057591942777</v>
+        <v>2.600274538246853</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.284766576384706</v>
+        <v>1.221424697225775</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.315193278413382</v>
+        <v>5.277188150918024</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963133</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.573113817172709</v>
+        <v>-4.652571451412518</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.701920054502589</v>
+        <v>2.670137000806665</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.491451050027081</v>
+        <v>1.42810917086815</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.42639263570167</v>
+        <v>5.388387508206312</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162543</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.607270712170235</v>
+        <v>-4.686728346410044</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.690258810157684</v>
+        <v>2.65847575646176</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.407867280486269</v>
+        <v>1.344525401327338</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.378243887631287</v>
+        <v>5.340238760135929</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.782482115652384</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.514681233108779</v>
+        <v>-4.594138867348588</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.080791715771934</v>
+        <v>3.04900866207601</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.407867280486269</v>
+        <v>1.344525401327338</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.731741001620954</v>
+        <v>5.693735874125596</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108672</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.574569860932329</v>
+        <v>-4.654027495172138</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.061399376209617</v>
+        <v>3.029616322513693</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.393745365798804</v>
+        <v>1.330403486639873</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.727830964375579</v>
+        <v>5.689825836880221</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.522353551135987</v>
+        <v>-4.601811185375796</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.132115841451681</v>
+        <v>3.100332787755757</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.393745365798804</v>
+        <v>1.330403486639873</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.777660905699107</v>
+        <v>5.739655778203749</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.490456034050742</v>
+        <v>-4.569913668290551</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.15368881849579</v>
+        <v>3.121905764799867</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.42564288288405</v>
+        <v>1.362301003725119</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.805613386160265</v>
+        <v>5.767608258664906</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650754</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.505211358250882</v>
+        <v>-4.584668992490691</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.143424272854931</v>
+        <v>3.111641219159007</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.42564288288405</v>
+        <v>1.362301003725119</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.801250970199462</v>
+        <v>5.763245842704103</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135749</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.455746734880971</v>
+        <v>-4.53520436912078</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.154134625619175</v>
+        <v>3.122351571923252</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.475107506253962</v>
+        <v>1.411765627095031</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.821854247637689</v>
+        <v>5.78384912014233</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479222</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.292638742727355</v>
+        <v>-4.372096376967164</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.215785490195556</v>
+        <v>3.184002436499632</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.638215498407577</v>
+        <v>1.574873619248646</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.916126710644792</v>
+        <v>5.878121583149434</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844247</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.159831117230189</v>
+        <v>-4.239288751469998</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.277955577085551</v>
+        <v>3.246172523389627</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.638215498407577</v>
+        <v>1.574873619248646</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.92517374733592</v>
+        <v>5.887168619840562</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.83242598779095</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.222539033704747</v>
+        <v>-4.301996667944556</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.253729875481849</v>
+        <v>3.221946821785926</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.575507581933019</v>
+        <v>1.512165702774088</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.888406462437308</v>
+        <v>5.850401334941949</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.899379203875191</v>
+        <v>3.735182608932476</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.140683023368438</v>
+        <v>-4.253988544100863</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.249381696406725</v>
+        <v>3.204059488113755</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.575507581933019</v>
+        <v>1.512165702774088</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.85131587922766</v>
+        <v>5.813310751732301</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240927.xlsx
+++ b/tame_output/ON/bt/strategyON_20240927.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>421.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.0%</t>
+          <t>-584.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-54.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.0%</t>
+          <t>-313.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-75.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.0%</t>
+          <t>131.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>119.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>135.3%</t>
+          <t>133.6%</t>
         </is>
       </c>
     </row>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.699856077053838</v>
+        <v>-3.79146445345088</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.054296584267048</v>
+        <v>1.017653233708232</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6247956396175203</v>
+        <v>0.5331872632204783</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.909472823172844</v>
+        <v>2.854507797334619</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.818236749783977</v>
+        <v>-3.909845126181019</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8453000351756463</v>
+        <v>0.8086566846168295</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.4659694110695021</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.707497831882912</v>
+        <v>2.652532806044686</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.926850828227308</v>
+        <v>-4.018459204624349</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9220040645175196</v>
+        <v>0.885360713958703</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.4659694110695021</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.827647492602118</v>
+        <v>2.772682466763892</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.891441789979165</v>
+        <v>-3.983050166376207</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9506807059190996</v>
+        <v>0.914037355360283</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.4659694110695021</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.842160518704441</v>
+        <v>2.787195492866215</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.899902958634626</v>
+        <v>-3.991511335031668</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9447156797992839</v>
+        <v>0.9080723292404673</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.549116618811083</v>
+        <v>0.457508242414041</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834503258853533</v>
+        <v>2.779538233015307</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.72278662859946</v>
+        <v>-3.814395004996502</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.012291240658653</v>
+        <v>0.975647890099836</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.549116618811083</v>
+        <v>0.457508242414041</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831232287698835</v>
+        <v>2.776267261860609</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.767878873433006</v>
+        <v>-3.859487249830047</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9949377344871477</v>
+        <v>0.9582943839283311</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4872205756416932</v>
+        <v>0.3956121992446512</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794778053559114</v>
+        <v>2.739813027720889</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.588503452194238</v>
+        <v>-3.680111828591279</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.060474878289069</v>
+        <v>1.023831527730253</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6439973338124119</v>
+        <v>0.55238895741537</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88263108376796</v>
+        <v>2.827666057929735</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.633517665714844</v>
+        <v>-3.725126042111885</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.023276648212416</v>
+        <v>0.9866332976535999</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6136484384978073</v>
+        <v>0.5220400621007654</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845229201910787</v>
+        <v>2.790264176072561</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.900522175987279</v>
+        <v>-3.992130552384321</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.922166406442388</v>
+        <v>0.8855230558835714</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4192854004548587</v>
+        <v>0.3276770240578168</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734302941423963</v>
+        <v>2.679337915585738</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.001719957424452</v>
+        <v>-4.093328333821494</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8808912157640203</v>
+        <v>0.8442478652052037</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.2592682105124976</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692461575193273</v>
+        <v>2.637496549355048</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.99520899081014</v>
+        <v>-4.086817367207181</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8810955639640621</v>
+        <v>0.8444522134052455</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.2592682105124976</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.69006153674759</v>
+        <v>2.635096510909364</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.976170863102842</v>
+        <v>-4.067779239499884</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8852355342552258</v>
+        <v>0.8485921836964092</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.2010845991813031</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651676089157118</v>
+        <v>2.596711063318893</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.028686665377663</v>
+        <v>-4.120295041774704</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9835236149794881</v>
+        <v>0.9468802644206715</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.2010845991813031</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770970490791308</v>
+        <v>2.716005464953083</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.151066053975958</v>
+        <v>-4.123703353209284</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9354051885263035</v>
+        <v>0.946350268832973</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2618676654287915</v>
+        <v>0.2336011681906804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75330863368771</v>
+        <v>2.736348735344843</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.131709918082111</v>
+        <v>-4.104347217315437</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9491561732807683</v>
+        <v>0.960101253587438</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2618676654287915</v>
+        <v>0.2336011681906804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.759317164084636</v>
+        <v>2.742357265741769</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.983966947847108</v>
+        <v>-3.956604247080434</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9062035826519688</v>
+        <v>0.9171486629586383</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4296750226636746</v>
+        <v>0.4014085254255636</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.757951799702765</v>
+        <v>2.740991901359898</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.067788169121807</v>
+        <v>-4.040425468355132</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8754687156735705</v>
+        <v>0.8864137959802401</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4296750226636746</v>
+        <v>0.4014085254255636</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.760745421234246</v>
+        <v>2.743785522891379</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.061635463069022</v>
+        <v>-4.034272762302348</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8785921464863427</v>
+        <v>0.8895372267930122</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4358277287164589</v>
+        <v>0.4075612314783479</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.765099393257575</v>
+        <v>2.748139494914708</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.078444761219524</v>
+        <v>-4.05108206045285</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8709489039662521</v>
+        <v>0.8818939842729216</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4190184305659573</v>
+        <v>0.3907519333278462</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.754094291107384</v>
+        <v>2.737134392764518</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.016146762443402</v>
+        <v>-3.988784061676728</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.962203657273522</v>
+        <v>0.9731487375801913</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4643126948403993</v>
+        <v>0.4360461976022883</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.847606403468871</v>
+        <v>2.830646505126004</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.814356564778244</v>
+        <v>-3.78699386401157</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8452117380537121</v>
+        <v>0.8561568183603816</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6623308870095537</v>
+        <v>0.6340643897714426</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.76870932048449</v>
+        <v>2.751749422141624</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.865243277464439</v>
+        <v>-3.837880576697765</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8951472853014095</v>
+        <v>0.906092365608079</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6114441743233592</v>
+        <v>0.5831776770852481</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.808467525194949</v>
+        <v>2.791507626852082</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.778632534814631</v>
+        <v>-3.751269834047958</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9444193184773759</v>
+        <v>0.9553643987840454</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6900699055285174</v>
+        <v>0.6618034082904064</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.870270700034087</v>
+        <v>2.853310801691221</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.838841832819916</v>
+        <v>-3.811479132053242</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9188715800999339</v>
+        <v>0.9298166604066034</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6298606075232329</v>
+        <v>0.6015941102851219</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.832681102055588</v>
+        <v>2.815721203712722</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.789655184135564</v>
+        <v>-3.762292483368891</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9370378576136029</v>
+        <v>0.9479829379202724</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6298606075232329</v>
+        <v>0.6015941102851219</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.831172720095517</v>
+        <v>2.81421282175265</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.745282052496996</v>
+        <v>-3.717919351730322</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9546499777044666</v>
+        <v>0.9655950580111361</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6742337391618015</v>
+        <v>0.6459672419236905</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.857659466514094</v>
+        <v>2.840699568171227</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.710550731178495</v>
+        <v>-3.683188030411821</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9629363003704576</v>
+        <v>0.9738813806771272</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6742337391618015</v>
+        <v>0.6459672419236905</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.852053260652684</v>
+        <v>2.835093362309818</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.662895000617439</v>
+        <v>-3.635532299850765</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9883803496226844</v>
+        <v>0.9993254299293541</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7218894697228572</v>
+        <v>0.6936229724847461</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.887028456017123</v>
+        <v>2.870068557674256</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.562376842118685</v>
+        <v>-3.53501414135201</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.033479986396911</v>
+        <v>1.044425066703581</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8224076282216117</v>
+        <v>0.7941411309835007</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.9522317244911</v>
+        <v>2.935271826148234</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.546471512686332</v>
+        <v>-3.519108811919658</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.026596790645724</v>
+        <v>1.037541870952394</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7432949675123728</v>
+        <v>0.7150284702742618</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.891518800541429</v>
+        <v>2.874558902198562</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.501633111077934</v>
+        <v>-3.47427041031126</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.048629853899712</v>
+        <v>1.059574934206382</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7478384004572423</v>
+        <v>0.7195719032191312</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.898342562918979</v>
+        <v>2.881382664576113</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.521131567319942</v>
+        <v>-3.493768866553268</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.044991411033987</v>
+        <v>1.055936491340657</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.699753759177338</v>
+        <v>0.6714872619392269</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.873652717782115</v>
+        <v>2.856692819439248</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.476928730234042</v>
+        <v>-3.449566029467368</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.068552148396184</v>
+        <v>1.079497228702854</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7439565962632384</v>
+        <v>0.7156900990251274</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.906054022561492</v>
+        <v>2.889094124218626</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.484488396071089</v>
+        <v>-3.457125695304414</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.063938282530613</v>
+        <v>1.074883362837283</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7987600002730577</v>
+        <v>0.7704935030349467</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.937346065436631</v>
+        <v>2.920386167093765</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.326196978531816</v>
+        <v>-3.298834277765142</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.178502614729362</v>
+        <v>1.189447695036031</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7987600002730577</v>
+        <v>0.7704935030349467</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.988593830619671</v>
+        <v>2.971633932276804</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.11855497489734</v>
+        <v>-3.091192274130666</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.260000120777405</v>
+        <v>1.270945201084075</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.006402003907534</v>
+        <v>0.9781355066694228</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.11161973739461</v>
+        <v>3.094659839051743</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.067522882174812</v>
+        <v>-3.040160181408138</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.275361186104686</v>
+        <v>1.286306266411356</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.057434096630062</v>
+        <v>1.029167599391951</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.137187221266397</v>
+        <v>3.12022732292353</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.002298701047606</v>
+        <v>-2.974936000280932</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.318638262648274</v>
+        <v>1.329583342954943</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.122658277757268</v>
+        <v>1.094391780519157</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.193509134035425</v>
+        <v>3.176549235692558</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.964871680976473</v>
+        <v>-2.937508980209798</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.329570042976008</v>
+        <v>1.340515123282677</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.127909815786449</v>
+        <v>1.099643318548338</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.192621029152214</v>
+        <v>3.175661130809348</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.963513696002927</v>
+        <v>-2.936150995236253</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.331370029296666</v>
+        <v>1.342315109603336</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.202247941324268</v>
+        <v>1.173981444086157</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.238480696806146</v>
+        <v>3.221520798463279</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.935100432903043</v>
+        <v>-2.907737732136369</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.50329310555783</v>
+        <v>1.5142381858645</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.143272378577839</v>
+        <v>1.115005881339728</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.363653130179499</v>
+        <v>3.346693231836633</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.860318171878031</v>
+        <v>-2.832955471111357</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.653318919185653</v>
+        <v>1.664263999492322</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.218054639602852</v>
+        <v>1.189788142364741</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.528635396012324</v>
+        <v>3.511675497669458</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.834234087614223</v>
+        <v>-2.806871386847549</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.655460528905035</v>
+        <v>1.666405609211704</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.218054639602852</v>
+        <v>1.189788142364741</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.520343372026183</v>
+        <v>3.503383473683316</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.746356174505102</v>
+        <v>-2.718993473738428</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.688804889732462</v>
+        <v>1.699749970039132</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.333980282026203</v>
+        <v>1.305713784788092</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.588091953063973</v>
+        <v>3.571132054721106</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.737463713111819</v>
+        <v>-2.710101012345145</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.709916280016567</v>
+        <v>1.720861360323237</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.333980282026203</v>
+        <v>1.305713784788092</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.605646358790764</v>
+        <v>3.588686460447898</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.905939830081697</v>
+        <v>-2.878577129315023</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.6343808806332</v>
+        <v>1.645325960939869</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.306032446309622</v>
+        <v>1.277765949071511</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.5807327047654</v>
+        <v>3.563772806422533</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.459683637452257</v>
+        <v>-2.432320936685583</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.794153054872837</v>
+        <v>1.805098135179507</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.211313776639989</v>
+        <v>1.183047279401878</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.505171200151482</v>
+        <v>3.488211301808616</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.436962533769105</v>
+        <v>-2.409599833002431</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.793905518843003</v>
+        <v>1.804850599149673</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.211313776639989</v>
+        <v>1.183047279401878</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.495835222648387</v>
+        <v>3.47887532430552</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.566164347063147</v>
+        <v>-2.538801646296473</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.901130919376555</v>
+        <v>1.912075999683225</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.082111963345947</v>
+        <v>1.053845466107836</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.577220260523131</v>
+        <v>3.560260362180264</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.592038745537173</v>
+        <v>-2.564676044770499</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.927858982480592</v>
+        <v>1.938804062787261</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.127023572057688</v>
+        <v>1.098757074819577</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.641245048243822</v>
+        <v>3.624285149900955</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.584984055321999</v>
+        <v>-2.557621354555325</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.927356214556206</v>
+        <v>1.938301294862876</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.134078262272862</v>
+        <v>1.105811765034751</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.642153218362471</v>
+        <v>3.625193320019604</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.558032830995511</v>
+        <v>-2.530670130228837</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.948142857931543</v>
+        <v>1.959087938238213</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.148958608300581</v>
+        <v>1.12069211106247</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.661087579623844</v>
+        <v>3.644127681280978</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.579577058826299</v>
+        <v>-2.552214358059624</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.123628298944188</v>
+        <v>2.134573379250857</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.148958608300581</v>
+        <v>1.12069211106247</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.845190711768804</v>
+        <v>3.828230813425937</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.601985176631171</v>
+        <v>-2.574622475864496</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.106781746725232</v>
+        <v>2.117726827031902</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.148958608300581</v>
+        <v>1.12069211106247</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.837307406671797</v>
+        <v>3.82034750832893</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.630209412208771</v>
+        <v>-2.602846711442097</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.097546052043829</v>
+        <v>2.108491132350499</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.16693536075189</v>
+        <v>1.138668863513779</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.850147457692219</v>
+        <v>3.833187559349353</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.639650338097301</v>
+        <v>-2.612287637330627</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.150023399410264</v>
+        <v>2.160968479716934</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.289362478295281</v>
+        <v>1.26109598105717</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.979857445940102</v>
+        <v>3.962897547597235</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.728526969265775</v>
+        <v>-2.701164268499101</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.117363841488176</v>
+        <v>2.128308921794845</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.200485847126807</v>
+        <v>1.172219349888696</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.929422561784318</v>
+        <v>3.912462663441452</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.804856946866681</v>
+        <v>-2.777494246100007</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.084943663341589</v>
+        <v>2.095888743648258</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.200485847126807</v>
+        <v>1.172219349888696</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.927534374678094</v>
+        <v>3.910574476335227</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.95981373226681</v>
+        <v>-2.932451031500136</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.017781178784399</v>
+        <v>2.028726259091069</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.045529061726678</v>
+        <v>1.017262564488567</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.829380533040878</v>
+        <v>3.812420634698011</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.121382157794065</v>
+        <v>-3.094019457027391</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.951587818783649</v>
+        <v>1.962532899090319</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9187461379287988</v>
+        <v>0.8904796406906877</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.751744788972303</v>
+        <v>3.734784890629436</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.229682819664184</v>
+        <v>-3.20232011889751</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.92134096090152</v>
+        <v>1.93228604120819</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9187461379287988</v>
+        <v>0.8904796406906877</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.764818195838222</v>
+        <v>3.747858297495355</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.247486791384929</v>
+        <v>-3.220124090618254</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.906224568996163</v>
+        <v>1.917169649302832</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8482115150235976</v>
+        <v>0.8199450177854866</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.714502618878041</v>
+        <v>3.697542720535174</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.275387578494402</v>
+        <v>-3.248024877727727</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.893588295279375</v>
+        <v>1.904533375586045</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8136145908806628</v>
+        <v>0.7853480936425518</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.692268505519282</v>
+        <v>3.675308607176415</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.397913681197295</v>
+        <v>-3.370550980430621</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.841342298175417</v>
+        <v>1.852287378482086</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6910884881777689</v>
+        <v>0.6628219909396579</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.615517287874744</v>
+        <v>3.598557389531878</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.628428177382884</v>
+        <v>-3.60106547661621</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.815842459291685</v>
+        <v>1.826787539598355</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4605739919921802</v>
+        <v>0.4323074947540692</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.543914549753895</v>
+        <v>3.526954651411028</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.977173262607328</v>
+        <v>-3.949810561840653</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.816656144203755</v>
+        <v>1.827601224510424</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3518260380732824</v>
+        <v>0.3235595408351714</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.618977496404403</v>
+        <v>3.602017598061537</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.131159680383468</v>
+        <v>-4.103796979616794</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.824041846238938</v>
+        <v>1.834986926545608</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3518260380732824</v>
+        <v>0.3235595408351714</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.687957765550043</v>
+        <v>3.670997867207177</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.335759115246477</v>
+        <v>-4.308396414479803</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.728253274413855</v>
+        <v>1.739198354720525</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3518260380732824</v>
+        <v>0.3235595408351714</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.674008967670164</v>
+        <v>3.657049069327297</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.588234269254201</v>
+        <v>-4.560871568487527</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.63913370186618</v>
+        <v>1.650078782172849</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3518260380732824</v>
+        <v>0.3235595408351714</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.685879456725578</v>
+        <v>3.668919558382711</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.881130025733613</v>
+        <v>-4.853767324966939</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.523185933793359</v>
+        <v>1.534131014100028</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3518260380732824</v>
+        <v>0.3235595408351714</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.687089991244521</v>
+        <v>3.670130092901655</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.067794153868421</v>
+        <v>-5.040431453101747</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.452642024766757</v>
+        <v>1.463587105073426</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3250870672487225</v>
+        <v>0.2968205700106115</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.675168350977107</v>
+        <v>3.65820845263424</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.213814840782383</v>
+        <v>-5.186452140015709</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.389311602737362</v>
+        <v>1.400256683044031</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3160039754548655</v>
+        <v>0.2877374782167545</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.664796348636982</v>
+        <v>3.647836450294116</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.305528849891969</v>
+        <v>-5.278166149125294</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.514830055792571</v>
+        <v>1.525775136099241</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3160039754548655</v>
+        <v>0.2877374782167545</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.827000405336026</v>
+        <v>3.81004050699316</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.337180508951938</v>
+        <v>-5.309817808185263</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.497016030132398</v>
+        <v>1.507961110439068</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3108355182104253</v>
+        <v>0.2825690209723143</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.818745968953177</v>
+        <v>3.80178607061031</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.406246563524875</v>
+        <v>-5.3788838627582</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.479619025871714</v>
+        <v>1.490564106178384</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2484646407168153</v>
+        <v>0.2201981434787043</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.791552860025502</v>
+        <v>3.774592961682635</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.508222685773283</v>
+        <v>-5.480859985006608</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.447754215428254</v>
+        <v>1.458699295734923</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1464885184684077</v>
+        <v>0.1182220212302967</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.73929282513236</v>
+        <v>3.722332926789493</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.398216402296061</v>
+        <v>-5.370853701529386</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.483909616063317</v>
+        <v>1.494854696369988</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1696930903856829</v>
+        <v>0.1414265931475719</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.7453684555269</v>
+        <v>3.728408557184034</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.255156826555135</v>
+        <v>-5.22779412578846</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.545383457081662</v>
+        <v>1.556328537388332</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1777065169756622</v>
+        <v>0.1494400197375512</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.754426522202862</v>
+        <v>3.737466623859995</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.953710101083297</v>
+        <v>-4.926347400316622</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.673223030152933</v>
+        <v>1.684168110459603</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4791532424474995</v>
+        <v>0.4508867452093884</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.9425554403685</v>
+        <v>3.925595542025634</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.978300345318481</v>
+        <v>-4.950937644551806</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.66435811021157</v>
+        <v>1.67530319051824</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4791532424474995</v>
+        <v>0.4508867452093884</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.943526618121211</v>
+        <v>3.926566719778344</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.927261969311961</v>
+        <v>-4.899899268545286</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.685616364993934</v>
+        <v>1.696561445300604</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4791532424474995</v>
+        <v>0.4508867452093884</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.944369522500966</v>
+        <v>3.927409624158099</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.88612267444533</v>
+        <v>-4.858759973678655</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.721110181814732</v>
+        <v>1.732055262121402</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5202925373141303</v>
+        <v>0.4920260400760192</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.98809119829509</v>
+        <v>3.971131299952224</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.78948776242669</v>
+        <v>-4.762125061660015</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.575948142746122</v>
+        <v>1.586893223052792</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6169274493327702</v>
+        <v>0.5886609520946592</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.862256141630209</v>
+        <v>3.845296243287342</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.720449751478222</v>
+        <v>-4.693087050711547</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.607065391199474</v>
+        <v>1.618010471506144</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6859654602812383</v>
+        <v>0.6576989630431272</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.907180992273254</v>
+        <v>3.890221093930387</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.55595341728726</v>
+        <v>-4.528590716520585</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.657290743951941</v>
+        <v>1.668235824258611</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8504617944722002</v>
+        <v>0.8221952972340891</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.990305611863914</v>
+        <v>3.973345713521047</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.478854815745388</v>
+        <v>-4.451492114978713</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.68731789500512</v>
+        <v>1.69826297531179</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8504617944722002</v>
+        <v>0.8221952972340891</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.989493322300343</v>
+        <v>3.972533423957477</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.489240010635277</v>
+        <v>-4.461877309868602</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.693032596174236</v>
+        <v>1.703977676480906</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8400765995823108</v>
+        <v>0.8118101023441998</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.993130984491482</v>
+        <v>3.976171086148615</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.507828169357502</v>
+        <v>-4.480465468590827</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.756434338461772</v>
+        <v>1.767379418768442</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8214884408600855</v>
+        <v>0.7932219436219745</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.052815095034572</v>
+        <v>4.035855196691705</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.508126716053538</v>
+        <v>-4.480764015286863</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.753183930601656</v>
+        <v>1.764129010908326</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8211898941640496</v>
+        <v>0.7929233969259386</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.049504977835249</v>
+        <v>4.032545079492382</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.40730358236311</v>
+        <v>-4.379940881596435</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.798044079017218</v>
+        <v>1.808989159323888</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8336541096484035</v>
+        <v>0.8053876124102924</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.061514402065253</v>
+        <v>4.044554503722386</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.216522221610703</v>
+        <v>-4.189159520844028</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.874485876796725</v>
+        <v>1.885430957103395</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.024435470400811</v>
+        <v>0.9961689731626997</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.17611247199524</v>
+        <v>4.159152573652373</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.109558863761281</v>
+        <v>-4.082196162994606</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.89710806567409</v>
+        <v>1.90805314598076</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.082900078360612</v>
+        <v>1.054633581122501</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.191028082508717</v>
+        <v>4.174068184165851</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.054228275859519</v>
+        <v>-4.026865575092843</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.954207237446853</v>
+        <v>1.965152317753523</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.138230666262374</v>
+        <v>1.109964169024263</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.259193371861834</v>
+        <v>4.242233473518967</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.042174148946556</v>
+        <v>-4.014811448179881</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.952715456113476</v>
+        <v>1.963660536420146</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.150284793175337</v>
+        <v>1.122018295937226</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.260112415911049</v>
+        <v>4.243152517568182</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.083329268514777</v>
+        <v>-4.055966567748102</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.938134038470324</v>
+        <v>1.949079118776994</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.109129673607116</v>
+        <v>1.080863176369005</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.237299974354253</v>
+        <v>4.220340076011386</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.015280705823247</v>
+        <v>-3.987918005056572</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.978204489424818</v>
+        <v>1.989149569731488</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.177178236298646</v>
+        <v>1.148911739060535</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.290980137847052</v>
+        <v>4.274020239504186</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.246881098992747</v>
+        <v>-4.219518398226072</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.905767002330612</v>
+        <v>1.916712082637282</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.177178236298646</v>
+        <v>1.148911739060535</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.311182808020646</v>
+        <v>4.29422290967778</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.296932644521966</v>
+        <v>-4.269569943755291</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.869352620185806</v>
+        <v>1.880297700492476</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.177178236298646</v>
+        <v>1.148911739060535</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.294789044087529</v>
+        <v>4.277829145744662</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.472039477098411</v>
+        <v>-4.444676776331736</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.759561800748695</v>
+        <v>1.770506881055365</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.177178236298646</v>
+        <v>1.148911739060535</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.255040957680995</v>
+        <v>4.238081059338128</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.275939323667888</v>
+        <v>-4.248576622901213</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.845024481117844</v>
+        <v>1.855969561424514</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.373278389729169</v>
+        <v>1.345011892491058</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.379723668736249</v>
+        <v>4.362763770393382</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.122913931554604</v>
+        <v>-4.095551230787929</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.005405637536063</v>
+        <v>2.016350717842732</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.526303781842453</v>
+        <v>1.498037284604342</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.570709903577124</v>
+        <v>4.553750005234257</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.151221245427874</v>
+        <v>-4.123858544661199</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.181548936895047</v>
+        <v>2.192494017201717</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.526303781842453</v>
+        <v>1.498037284604342</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.758176128485417</v>
+        <v>4.74121623014255</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.317814470541396</v>
+        <v>-4.290451769774721</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.084314598203721</v>
+        <v>2.095259678510391</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.35971055672893</v>
+        <v>1.331444059490819</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.627623144771386</v>
+        <v>4.610663246428519</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.29477867717983</v>
+        <v>-4.267415976413155</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.097205318210065</v>
+        <v>2.108150398516735</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.35971055672893</v>
+        <v>1.331444059490819</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.631299547433104</v>
+        <v>4.614339649090237</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.265532696724134</v>
+        <v>-4.238169995957459</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.106521765515839</v>
+        <v>2.117466845822509</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.35971055672893</v>
+        <v>1.331444059490819</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.628917602556599</v>
+        <v>4.611957704213732</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.372458244601985</v>
+        <v>-4.34509554383531</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.061044785522333</v>
+        <v>2.071989865829003</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.252785008851079</v>
+        <v>1.224518511612968</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.562055512987523</v>
+        <v>4.545095614644657</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.517476803109234</v>
+        <v>-4.490114102342559</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.004466164262668</v>
+        <v>2.015411244569338</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.107766450343831</v>
+        <v>1.07949995310572</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.476473180026408</v>
+        <v>4.459513281683542</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.635818568893951</v>
+        <v>-4.608455868127276</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.057060697206534</v>
+        <v>2.068005777513204</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.118452488906721</v>
+        <v>1.09018599166861</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.582816042421896</v>
+        <v>4.565856144079029</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.687228991214659</v>
+        <v>-4.659866290447984</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.03428222540419</v>
+        <v>2.04522730571086</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.118452488906721</v>
+        <v>1.09018599166861</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.580601739547834</v>
+        <v>4.563641841204968</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.766648442422411</v>
+        <v>-4.739285741655736</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.002417572995379</v>
+        <v>2.013362653302048</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.118452488906721</v>
+        <v>1.09018599166861</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.580504867622124</v>
+        <v>4.563544969279257</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.862111440339628</v>
+        <v>-4.834748739572953</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.964226267386534</v>
+        <v>1.975171347693204</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.118452488906721</v>
+        <v>1.09018599166861</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.580498761180166</v>
+        <v>4.5635388628373</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.797735529488913</v>
+        <v>-4.770372828722238</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.988073028289431</v>
+        <v>1.999018108596101</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.182828399757436</v>
+        <v>1.154561902519325</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.617220704253207</v>
+        <v>4.60026080591034</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.853104691621107</v>
+        <v>-4.825741990854432</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.97165918118428</v>
+        <v>1.98260426149095</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.182828399757436</v>
+        <v>1.154561902519325</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.622954522000933</v>
+        <v>4.605994623658066</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.871323158618716</v>
+        <v>-4.843960457852041</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.963910157728169</v>
+        <v>1.974855238034839</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.157721962501594</v>
+        <v>1.129455465263483</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.60742902299036</v>
+        <v>4.590469124647494</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.783116324471138</v>
+        <v>-4.755753623704463</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.019067284237519</v>
+        <v>2.030012364544189</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.157721962501594</v>
+        <v>1.129455465263483</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.627303415840679</v>
+        <v>4.610343517497812</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.677081329265828</v>
+        <v>-4.649718628499153</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.045181982844371</v>
+        <v>2.056127063151041</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.157721962501594</v>
+        <v>1.129455465263483</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.611004116365407</v>
+        <v>4.59404421802254</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.493869666132733</v>
+        <v>-4.466506965366058</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.120897597561654</v>
+        <v>2.131842677868324</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.157721962501594</v>
+        <v>1.129455465263483</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.613435065829452</v>
+        <v>4.596475167486585</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.422148219118882</v>
+        <v>-4.394785518352207</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.132530582446572</v>
+        <v>2.143475662753242</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.229443409515445</v>
+        <v>1.201176912277333</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.63941234011714</v>
+        <v>4.622452441774273</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.399775193511176</v>
+        <v>-4.372412492744501</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.088395538610825</v>
+        <v>2.099340618917496</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.240699160628346</v>
+        <v>1.212432663390235</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.593081536706052</v>
+        <v>4.576121638363185</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.432791489421921</v>
+        <v>-4.405428788655246</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.260387225131884</v>
+        <v>2.271332305438554</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.171261783961594</v>
+        <v>1.142995286723483</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.736617315591356</v>
+        <v>4.71965741724849</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.421263853772312</v>
+        <v>-4.393901153005637</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.256919505219976</v>
+        <v>2.267864585526646</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.230262442162957</v>
+        <v>1.201995944924846</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.763938936340423</v>
+        <v>4.746979037997557</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.518605355114681</v>
+        <v>-4.491242654348006</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.221651017204817</v>
+        <v>2.232596097511487</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.185842259997469</v>
+        <v>1.157575762759357</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.740954939562918</v>
+        <v>4.723995041220052</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.604461384454647</v>
+        <v>-4.577098683687972</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.188559687661669</v>
+        <v>2.199504767968339</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.143466190771333</v>
+        <v>1.115199693533222</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.716780380220076</v>
+        <v>4.699820481877209</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.613298181870767</v>
+        <v>-4.585935481104092</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.167444170515723</v>
+        <v>2.178389250822392</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.136024018129983</v>
+        <v>1.107757520891872</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.694734278455767</v>
+        <v>4.677774380112901</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.704680744436225</v>
+        <v>-4.67731804366955</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.141055656534589</v>
+        <v>2.152000736841258</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.099459133410638</v>
+        <v>1.071192636172527</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.68295985866921</v>
+        <v>4.665999960326343</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.692974026449219</v>
+        <v>-4.665611325682544</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.247866601553659</v>
+        <v>2.258811681860329</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.111165851397645</v>
+        <v>1.082899354159534</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.792112147285682</v>
+        <v>4.775152248942815</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.763886100191497</v>
+        <v>-4.736523399424822</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.222534110788153</v>
+        <v>2.233479191094823</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.111165851397645</v>
+        <v>1.082899354159534</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.795144486017087</v>
+        <v>4.77818458767422</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.774202198357849</v>
+        <v>-4.746839497591174</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.43131250479967</v>
+        <v>2.44225758510634</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.111165851397645</v>
+        <v>1.082899354159534</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.008049319295145</v>
+        <v>4.991089420952278</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.774108230340476</v>
+        <v>-4.746745529573801</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.430528758918709</v>
+        <v>2.441473839225379</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.007449903015625</v>
+        <v>4.990490004672758</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.922474457996621</v>
+        <v>-4.895111757229946</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.365414253800605</v>
+        <v>2.376359334107275</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.001681888959979</v>
+        <v>4.984721990617112</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.921526034878583</v>
+        <v>-4.894163334111908</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.36579362304782</v>
+        <v>2.37673870335449</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.001681888959979</v>
+        <v>4.984721990617112</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.021795852837604</v>
+        <v>-4.994433152070929</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.338413303845304</v>
+        <v>2.349358384151974</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.014409496941071</v>
+        <v>4.997449598598204</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.015803606048792</v>
+        <v>-4.988440905282117</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.342756200985216</v>
+        <v>2.353701281291886</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.016355495365459</v>
+        <v>4.999395597022592</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.927245644918025</v>
+        <v>-4.89988294415135</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.371833521455292</v>
+        <v>2.382778601761962</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.010009631383228</v>
+        <v>4.993049733040361</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.909486567414951</v>
+        <v>-4.882123866648276</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.378245829895517</v>
+        <v>2.389190910202188</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.111535712744963</v>
+        <v>1.083269215506852</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.009318308822223</v>
+        <v>4.992358410479357</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.809856416365883</v>
+        <v>-4.782493715599208</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.430880076223731</v>
+        <v>2.441825156530401</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.21116586379403</v>
+        <v>1.182899366555919</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.081878585360251</v>
+        <v>5.064918687017384</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.859255925054894</v>
+        <v>-4.831893224288219</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.600274538246853</v>
+        <v>2.611219618553523</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.221424697225775</v>
+        <v>1.193158199987664</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.277188150918024</v>
+        <v>5.260228252575157</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.652571451412518</v>
+        <v>-4.625208750645843</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.670137000806665</v>
+        <v>2.681082081113336</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.42810917086815</v>
+        <v>1.399842673630039</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.388387508206312</v>
+        <v>5.371427609863445</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.686728346410044</v>
+        <v>-4.659365645643369</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.65847575646176</v>
+        <v>2.66942083676843</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.344525401327338</v>
+        <v>1.316258904089227</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.340238760135929</v>
+        <v>5.323278861793062</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.594138867348588</v>
+        <v>-4.566776166581913</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.04900866207601</v>
+        <v>3.05995374238268</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.344525401327338</v>
+        <v>1.316258904089227</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.693735874125596</v>
+        <v>5.676775975782729</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.654027495172138</v>
+        <v>-4.626664794405463</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.029616322513693</v>
+        <v>3.040561402820363</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.330403486639873</v>
+        <v>1.302136989401762</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.689825836880221</v>
+        <v>5.672865938537354</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.601811185375796</v>
+        <v>-4.574448484609121</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.100332787755757</v>
+        <v>3.111277868062428</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.330403486639873</v>
+        <v>1.302136989401762</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.739655778203749</v>
+        <v>5.722695879860882</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.569913668290551</v>
+        <v>-4.542550967523876</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.121905764799867</v>
+        <v>3.132850845106537</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.362301003725119</v>
+        <v>1.334034506487008</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.767608258664906</v>
+        <v>5.75064836032204</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.584668992490691</v>
+        <v>-4.557306291724016</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.111641219159007</v>
+        <v>3.122586299465677</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.362301003725119</v>
+        <v>1.334034506487008</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.763245842704103</v>
+        <v>5.746285944361237</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.53520436912078</v>
+        <v>-4.507841668354104</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.122351571923252</v>
+        <v>3.133296652229922</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.411765627095031</v>
+        <v>1.38349912985692</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.78384912014233</v>
+        <v>5.766889221799464</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.372096376967164</v>
+        <v>-4.344733676200489</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.184002436499632</v>
+        <v>3.194947516806303</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.574873619248646</v>
+        <v>1.546607122010535</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.878121583149434</v>
+        <v>5.861161684806567</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.239288751469998</v>
+        <v>-4.211926050703322</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.246172523389627</v>
+        <v>3.257117603696297</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.574873619248646</v>
+        <v>1.546607122010535</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.887168619840562</v>
+        <v>5.870208721497695</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.301996667944556</v>
+        <v>-4.274633967177881</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.221946821785926</v>
+        <v>3.232891902092596</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.512165702774088</v>
+        <v>1.483899205535977</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.850401334941949</v>
+        <v>5.833441436599083</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.735182608932476</v>
+        <v>3.87231728794596</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.253988544100863</v>
+        <v>-4.226625843334188</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.204059488113755</v>
+        <v>3.215004568420425</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.512165702774088</v>
+        <v>1.483899205535977</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.813310751732301</v>
+        <v>5.796350853389435</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240927.xlsx
+++ b/tame_output/ON/bt/strategyON_20240927.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>179.4%</t>
+          <t>199.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.5%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.0%</t>
+          <t>-617.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-243.4%</t>
+          <t>-215.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.2%</t>
+          <t>-313.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.7%</t>
+          <t>134.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>-114.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>140.2%</t>
+          <t>147.0%</t>
         </is>
       </c>
     </row>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.415402646047523</v>
       </c>
       <c r="D1856" t="n">
         <v>-3.278314169314071</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.828177569167486</v>
+        <v>2.103720554008147</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.561409566444734</v>
       </c>
     </row>
     <row r="1857">
@@ -44259,19 +44259,19 @@
         <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.411508704703781</v>
       </c>
       <c r="D1857" t="n">
         <v>-3.484825946201093</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.741678917068935</v>
+        <v>2.017221901909596</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.433608558968779</v>
       </c>
     </row>
     <row r="1858">
@@ -44282,19 +44282,19 @@
         <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.413281631404041</v>
       </c>
       <c r="D1858" t="n">
         <v>-3.804170021281594</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.615714213736994</v>
+        <v>1.891257198577655</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.435381485669039</v>
       </c>
     </row>
     <row r="1859">
@@ -44305,19 +44305,19 @@
         <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.399614518871445</v>
       </c>
       <c r="D1859" t="n">
         <v>-4.190379852557369</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.447563168694089</v>
+        <v>1.72310615353475</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.367250609305977</v>
       </c>
     </row>
     <row r="1860">
@@ -44328,19 +44328,19 @@
         <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.387899293873536</v>
       </c>
       <c r="D1860" t="n">
         <v>-4.458931643255243</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.32842722741703</v>
+        <v>1.603970212257691</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.1179447876207835</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.041589436460405</v>
+        <v>3.317132421301066</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.386479885529501</v>
       </c>
       <c r="D1861" t="n">
         <v>-4.794594290485695</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.192742760180814</v>
+        <v>1.468285745021475</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.1858757731096883</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.999411436823027</v>
+        <v>3.274954421663688</v>
       </c>
     </row>
     <row r="1862">
@@ -44374,19 +44374,19 @@
         <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.392967445763742</v>
       </c>
       <c r="D1862" t="n">
         <v>-4.871038620688567</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.168652588333907</v>
+        <v>1.444195573174568</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.1054302640160264</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.054166302513466</v>
+        <v>3.329709287354127</v>
       </c>
     </row>
     <row r="1863">
@@ -44397,19 +44397,19 @@
         <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.392221960769574</v>
       </c>
       <c r="D1863" t="n">
         <v>-5.236166003327313</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.02185615028424</v>
+        <v>1.297399135124901</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4017410483150389</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.87563434693989</v>
+        <v>3.151177331780551</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.390983504784333</v>
       </c>
       <c r="D1864" t="n">
         <v>-5.644754780507992</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.857182183426727</v>
+        <v>1.132725168267388</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.629242624646241</v>
+        <v>2.904785609486903</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.386168937255793</v>
       </c>
       <c r="D1865" t="n">
         <v>-5.758515192530857</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.806863451089042</v>
+        <v>1.082406435929703</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.624428057117702</v>
+        <v>2.899971041958363</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.384162987864671</v>
       </c>
       <c r="D1866" t="n">
         <v>-6.174907066817855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.9138437368237815</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.622422107726579</v>
+        <v>2.897965092567241</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.39442167853335</v>
       </c>
       <c r="D1867" t="n">
         <v>-6.536080696634842</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.779632975565665</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.632680798395258</v>
+        <v>2.90822378323592</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.390521243679045</v>
       </c>
       <c r="D1868" t="n">
         <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.6384291328541529</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.628780363540954</v>
+        <v>2.904323348381615</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.388926163734046</v>
       </c>
       <c r="D1869" t="n">
         <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.6175529260122161</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.627185283595955</v>
+        <v>2.902728268436616</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.392705139663254</v>
       </c>
       <c r="D1870" t="n">
         <v>-7.094350693494567</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.5546084379516798</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.605594265297281</v>
+        <v>2.881137250137942</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.388678835128851</v>
       </c>
       <c r="D1871" t="n">
         <v>-7.28107040180387</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.4758942500935555</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.601567960762878</v>
+        <v>2.877110945603539</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.388576733807267</v>
       </c>
       <c r="D1872" t="n">
         <v>-7.664071790546501</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.322591593274919</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.601465859441294</v>
+        <v>2.877008844281955</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.391148249778697</v>
       </c>
       <c r="D1873" t="n">
         <v>-7.66855823574789</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.3233685311657934</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.601345508291891</v>
+        <v>2.876888493132552</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.396498553076747</v>
       </c>
       <c r="D1874" t="n">
         <v>-8.028088558251891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>0.1849067054622426</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.606695811589941</v>
+        <v>2.882238796430602</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.404414573033925</v>
       </c>
       <c r="D1875" t="n">
         <v>-8.078437621706113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>0.1726831000377316</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.584402393474585</v>
+        <v>2.859945378315246</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.407456323655694</v>
       </c>
       <c r="D1876" t="n">
         <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>0.1366771396909416</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.804415562484177</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.410349879977266</v>
       </c>
       <c r="D1877" t="n">
         <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>0.1179420962091706</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.774866219100734</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.415863077095908</v>
       </c>
       <c r="D1878" t="n">
         <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>0.1220249788911136</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.765062063069481</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.420345631580344</v>
       </c>
       <c r="D1879" t="n">
         <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>0.1130463979721603</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.709296596803694</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.435717333073765</v>
       </c>
       <c r="D1880" t="n">
         <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>0.07278365361803862</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.641216629525801</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.450272553821282</v>
       </c>
       <c r="D1881" t="n">
         <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>0.01728910741093825</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.550697199841392</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.443053388919686</v>
       </c>
       <c r="D1882" t="n">
         <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.0837108950964538</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.543478034939796</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.43638119814571</v>
       </c>
       <c r="D1883" t="n">
         <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.1321329782810086</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.474181005549952</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.437496987984266</v>
       </c>
       <c r="D1884" t="n">
         <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.1960225747218858</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.416716737137296</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.440190716613381</v>
       </c>
       <c r="D1885" t="n">
         <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.2437435634400869</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.434561439452256</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.444181052299782</v>
       </c>
       <c r="D1886" t="n">
         <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.216924518995314</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.438551775138657</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.44270582540104</v>
       </c>
       <c r="D1887" t="n">
         <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.2750684825837038</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.437076548239915</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.457759235565912</v>
       </c>
       <c r="D1888" t="n">
         <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.2401787346488975</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.481884465059688</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.444708101919229</v>
       </c>
       <c r="D1889" t="n">
         <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.1936625345068381</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.487583085854109</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.454287174955438</v>
       </c>
       <c r="D1890" t="n">
         <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.09374540038286439</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.522318164242616</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.455426319511497</v>
       </c>
       <c r="D1891" t="n">
         <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.04277479329176881</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.523457308798675</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.458060093673605</v>
       </c>
       <c r="D1892" t="n">
         <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.03012634650225721</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.541288535491224</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.463793797912241</v>
       </c>
       <c r="D1893" t="n">
         <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>0.004460627851531562</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.54702223972986</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.454056535518376</v>
       </c>
       <c r="D1894" t="n">
         <v>-8.576075471757756</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2522730623391358</v>
+        <v>0.02326992250152538</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.456586204360987</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.304561828061122</v>
+        <v>2.580104812901784</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.444173054205468</v>
       </c>
       <c r="D1895" t="n">
         <v>-8.482616437772531</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2247729300579535</v>
+        <v>0.05077005478270769</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.456586204360987</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.294678346748215</v>
+        <v>2.570221331588876</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.442338493706095</v>
       </c>
       <c r="D1896" t="n">
         <v>-8.4719632562191</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2223462179359545</v>
+        <v>0.05319676690470665</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.456586204360987</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.292843786248842</v>
+        <v>2.568386771089503</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.442038178732634</v>
       </c>
       <c r="D1897" t="n">
         <v>-8.374056217542609</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1834837174388193</v>
+        <v>0.09205926740184189</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.388600454500431</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.333334921191714</v>
+        <v>2.608877906032375</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.442706684878127</v>
       </c>
       <c r="D1898" t="n">
         <v>-8.350102676566651</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1732337949029423</v>
+        <v>0.1023091899377189</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.364646913524473</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.348375551922782</v>
+        <v>2.623918536763444</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.429446368716375</v>
       </c>
       <c r="D1899" t="n">
         <v>-8.086042738243854</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08087013573557567</v>
+        <v>0.1946728491050855</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.100586975201677</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.769094183595369</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.426659335056074</v>
       </c>
       <c r="D1900" t="n">
         <v>-7.378963114739016</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1991746800060588</v>
+        <v>0.47471766484672</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.100586975201677</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.766307149935068</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.427002958943916</v>
       </c>
       <c r="D1901" t="n">
         <v>-7.338778816372826</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.4911350080810375</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.790761352842624</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.426369780164673</v>
       </c>
       <c r="D1902" t="n">
         <v>-7.175378945433463</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.5558617776775394</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.888168096626999</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.434294209002525</v>
       </c>
       <c r="D1903" t="n">
         <v>-7.017261566054688</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3514901734262406</v>
+        <v>0.6270331582669018</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.7388854265173482</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.715419968251455</v>
+        <v>2.990962953092116</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.431401998689566</v>
       </c>
       <c r="D1904" t="n">
         <v>-6.867595175047173</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4084645195162873</v>
+        <v>0.6840075043569485</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6459819352748123</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.768269852684018</v>
+        <v>3.043812837524679</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>3.332662784696721</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.735319701416286</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3626354949757968</v>
+        <v>0.638178479816458</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5137064616439256</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.748895922869704</v>
+        <v>3.024438907710365</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>3.335477845384357</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.563458485851384</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4341950418893945</v>
+        <v>0.7097380267300557</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3418452460790228</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.854827712896283</v>
+        <v>3.130370697736944</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>3.348384186608016</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.478493819122065</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4810872498047809</v>
+        <v>0.7566302346454421</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2568805793497032</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.918712854157533</v>
+        <v>3.194255838998194</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>3.220408257008797</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.584083808895169</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3108753242963203</v>
+        <v>0.5864183091369815</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3624705691228076</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727382930694452</v>
+        <v>3.002925915535113</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>3.268952598885884</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.515849224269742</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3867135000235775</v>
+        <v>0.6622564848642387</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3440552462502716</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.78697646629506</v>
+        <v>3.062519451135721</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>3.152331790247477</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.367909182862142</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3292687079482102</v>
+        <v>0.6048116927888714</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.323734330341714</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.682548207201787</v>
+        <v>2.958091192042449</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>3.143617803993998</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.314939660608154</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3417425305963278</v>
+        <v>0.617285515436989</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.705615934300702</v>
+        <v>2.981158919141364</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>3.136657191898905</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.149151464647863</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4010971968853507</v>
+        <v>0.6766401817260119</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.698655322205609</v>
+        <v>2.974198307046271</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>3.151119546280048</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.115788258169094</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4289048338580015</v>
+        <v>0.7044478186986627</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713117676586752</v>
+        <v>2.988660661427414</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>3.145651666739243</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.007529121046573</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4667406091662052</v>
+        <v>0.7422835940068664</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.707649797045947</v>
+        <v>2.983192781886609</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>3.14314976074982</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.884237986229442</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5135551571036343</v>
+        <v>0.7890981419442955</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1474736732705946</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779122571946802</v>
+        <v>3.054665556787464</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>3.150850738987145</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.831541119098151</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5423348821934759</v>
+        <v>0.8178778670341371</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09477680613930345</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.818441670462903</v>
+        <v>3.093984655303564</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>3.146631447334196</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.587775677114706</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356217673339044</v>
+        <v>0.9111647521745656</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09477680613930345</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814222378809953</v>
+        <v>3.089765363650614</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>3.148755761254212</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.498000004738234</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6736563502045092</v>
+        <v>0.9491993350451704</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853306359678555</v>
+        <v>3.128849344519216</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>3.141497836237914</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.248149610789159</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7663385827678413</v>
+        <v>1.041881567608502</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846048434662257</v>
+        <v>3.121591419502919</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>3.145096959758563</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.072257518321727</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8402945432754629</v>
+        <v>1.115837528116124</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.849647558182906</v>
+        <v>3.125190543023567</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>3.158424465813117</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.900811055299264</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9222006345390019</v>
+        <v>1.197743619379663</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1382691017974697</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.965842942050938</v>
+        <v>3.241385926891599</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>3.157444943429414</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.820788768190143</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9532300269989473</v>
+        <v>1.228773011839609</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2182913889065907</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.012876791932707</v>
+        <v>3.288419776773368</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>3.162139744483731</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.757153025956208</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9833791249468384</v>
+        <v>1.2589221097875</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2819271311405252</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.055753038327385</v>
+        <v>3.331296023168046</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>3.143334003267527</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.663455707739813</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.002052311017192</v>
+        <v>1.277595295857853</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2819271311405252</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.036947297111181</v>
+        <v>3.312490281951842</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>3.145077079892404</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.673958330805102</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9995943384159538</v>
+        <v>1.275137323256615</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2714245080752363</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032388799896885</v>
+        <v>3.307931784737546</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>3.149006393727224</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.561472070136228</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.048518156518324</v>
+        <v>1.324061141358985</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2714245080752363</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036318113731705</v>
+        <v>3.311861098572366</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>3.149684977644564</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.543758383258362</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05628221518681</v>
+        <v>1.331825200027471</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2746058369721531</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.038905494987195</v>
+        <v>3.314448479827856</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>3.146683048864558</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.420284111945344</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.102669994932011</v>
+        <v>1.378212979772672</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2746058369721531</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.035903566207188</v>
+        <v>3.31144655104785</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>3.148262085875172</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.200263313908334</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.192257351157429</v>
+        <v>1.46780033599809</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4158256820401334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122214510258591</v>
+        <v>3.397757495099252</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>3.164156268676995</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.067395624845056</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.261298609584564</v>
+        <v>1.536841594425225</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4158256820401334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138108693060414</v>
+        <v>3.413651677901075</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>3.165302113117297</v>
       </c>
       <c r="D1931" t="n">
         <v>-3.947222541480557</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.310513687370665</v>
+        <v>1.586056672211326</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5359987654046323</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211358387519415</v>
+        <v>3.486901372360077</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>3.175390215678737</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.81196918015058</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.374703134464096</v>
+        <v>1.650246119304757</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6712521267346094</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.302598506878842</v>
+        <v>3.578141491719503</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>3.161427707080163</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.871844007508273</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336790694922444</v>
+        <v>1.612333679763106</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6113772993769173</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.252711101865652</v>
+        <v>3.528254086706313</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>3.176716876314371</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.752023776597435</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.400007956520988</v>
+        <v>1.675550941361649</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6113772993769173</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268000271099861</v>
+        <v>3.543543255940522</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>3.084361075636813</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.754493483059241</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.306664273258707</v>
+        <v>1.582207258099368</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6089075929151111</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174162646545219</v>
+        <v>3.44970563138588</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>3.003622937122114</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.822863669383251</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198578060214404</v>
+        <v>1.474121045055066</v>
       </c>
       <c r="F1936" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.098989927452249</v>
+        <v>3.37453291229291</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.994059645754005</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.934735949009402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144265856995835</v>
+        <v>1.419808841836497</v>
       </c>
       <c r="F1937" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.08942663608414</v>
+        <v>3.364969620924801</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.685091185837372</v>
+        <v>2.960634170678033</v>
       </c>
       <c r="D1938" t="n">
         <v>-3.918761283523134</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.11723024811437</v>
+        <v>1.392773232955031</v>
       </c>
       <c r="F1938" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.056001161008167</v>
+        <v>3.331544145848829</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.689658417829159</v>
+        <v>2.965201402669821</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.743287023730665</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.191987184023146</v>
+        <v>1.467530168863807</v>
       </c>
       <c r="F1939" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.060568392999955</v>
+        <v>3.336111377840616</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.665400446590366</v>
+        <v>2.940943431431028</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.73536264914575</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.170898962618318</v>
+        <v>1.44644194745898</v>
       </c>
       <c r="F1940" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.036310421761162</v>
+        <v>3.311853406601823</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.593938759991816</v>
+        <v>2.869481744832477</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.729084446575901</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.101948557047708</v>
+        <v>1.377491541888369</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.968615656704522</v>
+        <v>3.244158641545183</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264167</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.604111146423949</v>
+        <v>2.87965413126461</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.669231827372178</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.136061991161329</v>
+        <v>1.41160497600199</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.978788043136654</v>
+        <v>3.254331027977315</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742303</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.599057416997809</v>
+        <v>2.87460040183847</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.582988364345801</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165505646945741</v>
+        <v>1.441048631786402</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.973734313710514</v>
+        <v>3.249277298551176</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.590833192442334</v>
+        <v>2.866376177282996</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.628295183744781</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.139158694630674</v>
+        <v>1.414701679471335</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5836513315119443</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.941023991349501</v>
+        <v>3.216566976190162</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.591385065475436</v>
+        <v>2.866928050316097</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.657328288447082</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.128097325782855</v>
+        <v>1.403640310623516</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5836513315119443</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.941575864382603</v>
+        <v>3.217118849223264</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.520657757366802</v>
+        <v>2.796200742207463</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.564517806996223</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.094494210254565</v>
+        <v>1.370037195095226</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6764618129628036</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.926534845144484</v>
+        <v>3.202077829985145</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.522531233291402</v>
+        <v>2.798074218132064</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.608907276325651</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.078611898447394</v>
+        <v>1.354154883288055</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6320723436333759</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.901774639471428</v>
+        <v>3.17731762431209</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.517606941803125</v>
+        <v>2.793149926643787</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.588403582440153</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.081889084513316</v>
+        <v>1.357432069353977</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6525760375188733</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.90915256431445</v>
+        <v>3.184695549155111</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.523098237633793</v>
+        <v>2.798641222474454</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.672075679152485</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.053911541659051</v>
+        <v>1.329454526499712</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6525760375188733</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.914643860145117</v>
+        <v>3.190186844985778</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.534595439402332</v>
+        <v>2.810138424242993</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.699856077053838</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.054296584267048</v>
+        <v>1.32983956910771</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6247956396175203</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.909472823172844</v>
+        <v>3.185015808013505</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.372951159402985</v>
+        <v>2.648494144243646</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.818236749783977</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8453000351756463</v>
+        <v>1.120843020016308</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.707497831882912</v>
+        <v>2.983040816723573</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.493100820122191</v>
+        <v>2.768643804962852</v>
       </c>
       <c r="D1952" t="n">
         <v>-3.926850828227308</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9220040645175196</v>
+        <v>1.197547049358181</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.827647492602118</v>
+        <v>3.103190477442779</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.507613846224514</v>
+        <v>2.783156831065175</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.891441789979165</v>
+        <v>-3.994961385368801</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9506807059190996</v>
+        <v>1.184815852603907</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.842160518704441</v>
+        <v>3.117703503545102</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.505033287566882</v>
+        <v>2.780576272407544</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.899902958634626</v>
+        <v>-4.003422554024262</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9447156797992839</v>
+        <v>1.178850826484091</v>
       </c>
       <c r="F1954" t="n">
         <v>0.549116618811083</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834503258853533</v>
+        <v>3.110046243694194</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.501762316412185</v>
+        <v>2.777305301252846</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.72278662859946</v>
+        <v>-3.826306223989095</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.012291240658653</v>
+        <v>1.24642638734346</v>
       </c>
       <c r="F1955" t="n">
         <v>0.549116618811083</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831232287698835</v>
+        <v>3.106775272539496</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.502445708174098</v>
+        <v>2.777988693014759</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.767878873433006</v>
+        <v>-3.871398468822641</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9949377344871477</v>
+        <v>1.229072881171954</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4872205756416932</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794778053559114</v>
+        <v>3.070321038399775</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.496232683480512</v>
+        <v>2.771775668321173</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.588503452194238</v>
+        <v>-3.692023047583873</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.060474878289069</v>
+        <v>1.294610024973876</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6439973338124119</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88263108376796</v>
+        <v>3.158174068608621</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.477040138812102</v>
+        <v>2.752583123652763</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.633517665714844</v>
+        <v>-3.737037261104479</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.023276648212416</v>
+        <v>1.257411794897223</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6136484384978073</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845229201910787</v>
+        <v>3.120772186751448</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.482731701151048</v>
+        <v>2.758274685991709</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.900522175987279</v>
+        <v>-4.004041771376915</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.922166406442388</v>
+        <v>1.156301553127195</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4192854004548587</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734302941423963</v>
+        <v>3.009845926264624</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.481935623047549</v>
+        <v>2.75747860788821</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.001719957424452</v>
+        <v>-4.105239552814088</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8808912157640203</v>
+        <v>1.115026362448827</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3508765869095395</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692461575193273</v>
+        <v>2.968004560033934</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.479535584601866</v>
+        <v>2.755078569442527</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.99520899081014</v>
+        <v>-4.098728586199775</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8810955639640621</v>
+        <v>1.115230710648869</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3508765869095395</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.69006153674759</v>
+        <v>2.965604521588251</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.476060303810111</v>
+        <v>2.751603288650772</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.976170863102842</v>
+        <v>-4.079690458492478</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8852355342552258</v>
+        <v>1.119370680940033</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2926929755783449</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651676089157118</v>
+        <v>2.927219073997779</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.595354705444301</v>
+        <v>2.870897690284962</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.028686665377663</v>
+        <v>-4.132206260767298</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9835236149794881</v>
+        <v>1.217658761664295</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2926929755783449</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770970490791308</v>
+        <v>3.046513475631969</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.596188034430435</v>
+        <v>2.871731019271096</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.032094976812242</v>
+        <v>-4.135614572201878</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9829936193917896</v>
+        <v>1.217128766076597</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3252095445877223</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.791313761183068</v>
+        <v>3.066856746023729</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.602196564827361</v>
+        <v>2.877739549668022</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.092954865157068</v>
+        <v>-4.116258436308031</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9646581944507857</v>
+        <v>1.230879750831062</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3252095445877223</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.797322291579994</v>
+        <v>3.072865276420655</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.50014678610456</v>
+        <v>2.775689770945221</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.945211894922065</v>
+        <v>-3.968515466073029</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.921705603821986</v>
+        <v>1.187927160202262</v>
       </c>
       <c r="F1966" t="n">
         <v>0.4930169018226055</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795956927198123</v>
+        <v>3.071499912038785</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.502940407636041</v>
+        <v>2.778483392476702</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.029033116196763</v>
+        <v>-4.052336687347727</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8909707368435877</v>
+        <v>1.157192293223864</v>
       </c>
       <c r="F1967" t="n">
         <v>0.4930169018226055</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798750548729604</v>
+        <v>3.074293533570266</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.779145740868361</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.022880410143979</v>
+        <v>-4.046183981294942</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8940941676563599</v>
+        <v>1.160315724036636</v>
       </c>
       <c r="F1968" t="n">
         <v>0.4991696078753898</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.803104520752933</v>
+        <v>3.078647505593595</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.778226217608471</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.039689708294481</v>
+        <v>-4.062993279445444</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8864509251362693</v>
+        <v>1.152672481516545</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4823603097248881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.792099418602743</v>
+        <v>3.067642403443404</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.844561771405292</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.977391709518359</v>
+        <v>-4.000695280669323</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.977705678443539</v>
+        <v>1.243927234823815</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5276545739993301</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.885611530964229</v>
+        <v>3.16115451580489</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.646853773119419</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.775601511853201</v>
+        <v>-4.015740698081363</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8607137592237293</v>
+        <v>1.040201069573126</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7256727661684845</v>
+        <v>0.5594005889811819</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.806714447979849</v>
+        <v>2.982494126508128</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.717144005441594</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.826488224539396</v>
+        <v>-4.066627410767557</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9106493064714265</v>
+        <v>1.090136616820824</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.67478605348229</v>
+        <v>0.5085138762949875</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846472652690307</v>
+        <v>3.022252331218587</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.731771741557638</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.739877481889589</v>
+        <v>-3.98001666811775</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9599213396473931</v>
+        <v>1.13940864999679</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7534117846874483</v>
+        <v>0.5871396075001457</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.908275827529446</v>
+        <v>3.084055506057725</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.730307722382309</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.800086779894873</v>
+        <v>-4.040225966123034</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9343736012699511</v>
+        <v>1.113860911619348</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.5269303094948612</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.870686229550947</v>
+        <v>3.046465908079226</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.728799340422238</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.750900131210522</v>
+        <v>-3.991039317438683</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9525398787836201</v>
+        <v>1.132027189133017</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.5269303094948612</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.869177847590875</v>
+        <v>3.044957526119155</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.728662207857674</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.706526999571953</v>
+        <v>-3.946666185800114</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9701519988744838</v>
+        <v>1.149639309223881</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.5713034411334298</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.895664594009453</v>
+        <v>3.071444272537732</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.723056001996265</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.671795678253452</v>
+        <v>-3.911934864481613</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9784383215404746</v>
+        <v>1.157925631889872</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.5713034411334298</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.890058388148043</v>
+        <v>3.065838066676323</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.729437759024069</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.624139947692396</v>
+        <v>-3.864279133920558</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.003882370792702</v>
+        <v>1.183369681142098</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.785231348881788</v>
+        <v>0.6189591716944854</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.925033583512481</v>
+        <v>3.100813262040761</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.734330132398794</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.523621789193641</v>
+        <v>-3.763760975421803</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.048982007566928</v>
+        <v>1.228469317916325</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8857495073805426</v>
+        <v>0.71947733019324</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.990236851986459</v>
+        <v>3.166016530514738</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.721084804874666</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.507716459761289</v>
+        <v>-3.747855645989451</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.042098811815741</v>
+        <v>1.221586122165138</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8066368466713036</v>
+        <v>0.6403646694840011</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929523928036788</v>
+        <v>3.105303606565067</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.725182507485295</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.462878058152891</v>
+        <v>-3.703017244381053</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.064131875069729</v>
+        <v>1.243619185419126</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8111802796161731</v>
+        <v>0.6449081024288705</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936347690414338</v>
+        <v>3.112127368942617</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.729343447116373</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.482376514394899</v>
+        <v>-3.722515700623061</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.060493432204004</v>
+        <v>1.239980742553401</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7630956383362688</v>
+        <v>0.5968234611489662</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.911657845277473</v>
+        <v>3.087437523805753</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.73522304964421</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.438173677308999</v>
+        <v>-3.67831286353716</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.084054169566201</v>
+        <v>1.263541479915598</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8072984754221693</v>
+        <v>0.6410262982348667</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.944059150056851</v>
+        <v>3.11983882858513</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.733633050113458</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.445733343146046</v>
+        <v>-3.685872529374207</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.07944030370063</v>
+        <v>1.258927614050027</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.695829702244686</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.97535119293199</v>
+        <v>3.151130871460269</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284881</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.784880815296497</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.287441925606773</v>
+        <v>-3.527581111834935</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.194004635899379</v>
+        <v>1.373491946248776</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.695829702244686</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.026598958115029</v>
+        <v>3.202378636643309</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.78332151989075</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.079799921972297</v>
+        <v>-3.319939108200459</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.275502141947422</v>
+        <v>1.454989452296819</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.069743883066465</v>
+        <v>0.9034717058791621</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.149624864889968</v>
+        <v>3.325404543418248</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.77826974812902</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.028767829249769</v>
+        <v>-3.268907015477931</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.290863207274703</v>
+        <v>1.4703505176241</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.120775975788993</v>
+        <v>0.9545037986016901</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175192348761755</v>
+        <v>3.350972027290035</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.795457152221725</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.963543648122563</v>
+        <v>-3.203682834350725</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.334140283818291</v>
+        <v>1.513627594167688</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.186000156916198</v>
+        <v>1.019727979728896</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.231514261530783</v>
+        <v>3.407293940059063</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.791418124521006</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.926116628051429</v>
+        <v>-3.166255814279591</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.345072064146025</v>
+        <v>1.524559374495422</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19125169494538</v>
+        <v>1.024979517758077</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.230626156647573</v>
+        <v>3.406405835175852</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.792674916852246</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.924758643077884</v>
+        <v>-3.164897829306046</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.346872050466683</v>
+        <v>1.52635936081608</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.265589820483199</v>
+        <v>1.099317643295896</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.276485824301504</v>
+        <v>3.452265502829784</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.953232687873457</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.896345379978</v>
+        <v>-3.136484566206162</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.518795126727847</v>
+        <v>1.698282437077244</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.20661425773677</v>
+        <v>1.040342080549467</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.401658257674858</v>
+        <v>3.577437936203137</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>3.073345597091274</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.821563118952988</v>
+        <v>-3.06170230518115</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.66882094035567</v>
+        <v>1.848308250705067</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.281396518761783</v>
+        <v>1.11512434157448</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.566640523507683</v>
+        <v>3.742420202035962</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>3.065053573105133</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.79547903468918</v>
+        <v>-3.035618220917342</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.670962550075052</v>
+        <v>1.850449860424449</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.281396518761783</v>
+        <v>1.11512434157448</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.558348499521542</v>
+        <v>3.734128178049821</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>3.063246768688912</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.707601121580059</v>
+        <v>-2.947740307808221</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.70430691090248</v>
+        <v>1.883794221251876</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.397322161185134</v>
+        <v>1.231049983997831</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626097080559332</v>
+        <v>3.801876759087611</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>3.080801174415704</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.698708660186776</v>
+        <v>-2.938847846414938</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.725418301186584</v>
+        <v>1.904905611535981</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.397322161185134</v>
+        <v>1.231049983997831</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.643651486286123</v>
+        <v>3.819431164814402</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>3.072656221820288</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.867184777156654</v>
+        <v>-3.107323963384816</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.649882901803217</v>
+        <v>1.829370212152614</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.369374325468553</v>
+        <v>1.20310214828125</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.618737832260758</v>
+        <v>3.794517510789038</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>3.05392591900815</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.420928584527214</v>
+        <v>-2.661067770755376</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.809655076042855</v>
+        <v>1.989142386392252</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.27465565579892</v>
+        <v>1.108383478611617</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.543176327646841</v>
+        <v>3.71895600617512</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>3.044589941505054</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.398207480844062</v>
+        <v>-2.638346667072224</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.80940754001302</v>
+        <v>1.988894850362417</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.27465565579892</v>
+        <v>1.108383478611617</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533840350143745</v>
+        <v>3.709620028672025</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>3.203496067356223</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.527409294138104</v>
+        <v>-2.767548480366266</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.916632940546572</v>
+        <v>2.096120250895969</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.145453842504878</v>
+        <v>0.9791816653175751</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.615225388018489</v>
+        <v>3.791005066546768</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>3.24057388984987</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.55328369261213</v>
+        <v>-2.793422878840292</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.943361003650609</v>
+        <v>2.122848314000005</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.190365451216619</v>
+        <v>1.024093274029316</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67925017573918</v>
+        <v>3.855029854267459</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>3.237249245839415</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.546229002396956</v>
+        <v>-2.786368188625118</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.942858235726223</v>
+        <v>2.12234554607562</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.197420141431793</v>
+        <v>1.03114796424449</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.855938024386109</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>3.247255399484156</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.519277778070468</v>
+        <v>-2.75941696429863</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.96364487910156</v>
+        <v>2.143132189450957</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.212300487459512</v>
+        <v>1.046028310272209</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.874872385647482</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.354174628652263</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.540822005901255</v>
+        <v>-2.876792556546279</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.139130320114205</v>
+        <v>2.203101181720004</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.212300487459512</v>
+        <v>1.046028310272209</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.981791614815589</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.346291323555256</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.563230123706127</v>
+        <v>-2.899200674351151</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.122283767895249</v>
+        <v>2.186254629501049</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.212300487459512</v>
+        <v>1.046028310272209</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.973908309718582</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.348345323104894</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.591454359283728</v>
+        <v>-2.927424909928751</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.113048073213847</v>
+        <v>2.177018934819646</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.230277239910821</v>
+        <v>1.064005062723518</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.986748360739004</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.404599040826741</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.600895285172258</v>
+        <v>-2.936865835817281</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.165525420580281</v>
+        <v>2.229496282186081</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.352704357454212</v>
+        <v>1.186432180266909</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>4.116458348986887</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.407490135372042</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.689771916340732</v>
+        <v>-3.025742466985755</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.132865862658193</v>
+        <v>2.196836724263992</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>1.097555549098435</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>4.066023464831103</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.405601948265817</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.766101893941638</v>
+        <v>-3.102072444586661</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.100445684511606</v>
+        <v>2.164416546117405</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>1.097555549098435</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>4.064135277724878</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.400422177868679</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.921058679341767</v>
+        <v>-3.25702922998679</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.033283199954417</v>
+        <v>2.097254061560216</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.108870940885609</v>
+        <v>0.9425987636983062</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.867385660536237</v>
+        <v>3.965981436087663</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.398856188078831</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.082627104869022</v>
+        <v>-3.418597655514045</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.967089839953667</v>
+        <v>2.031060701559466</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.8158158399004268</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.789749916467661</v>
+        <v>3.888345692019088</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.41192959494475</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.190927766739141</v>
+        <v>-3.526898317384165</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.936842982071537</v>
+        <v>2.000813843677337</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.8158158399004268</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.80282332333358</v>
+        <v>3.901419098885007</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.40393479172769</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.208731738459885</v>
+        <v>-3.544702289104909</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.92172659016618</v>
+        <v>1.985697451771979</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9115533941825285</v>
+        <v>0.7452812169952256</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.851103521924826</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.402458832854692</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.236632525569358</v>
+        <v>-3.572603076214382</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.909090316449393</v>
+        <v>1.973061178055191</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8769564700395936</v>
+        <v>0.7106842928522908</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.828869408566067</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.399223276831891</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.359158628272252</v>
+        <v>-3.695129178917276</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.856844319345434</v>
+        <v>1.920815180951233</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7544303673366998</v>
+        <v>0.588158190149397</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.752118190921529</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.465929236422395</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.589673124457841</v>
+        <v>-3.925643675102864</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.831344480461702</v>
+        <v>1.895315342067501</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.523915871151111</v>
+        <v>0.3576436939638082</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.68051545280068</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.606240955424242</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.938418209682284</v>
+        <v>-4.274388760327308</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.832158165373772</v>
+        <v>1.896129026979571</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.2488957400449104</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.755578399451188</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.675221224569881</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.092404627458425</v>
+        <v>-4.428375178103448</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.839543867408955</v>
+        <v>1.903514729014754</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.2488957400449104</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.824558668596828</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.661272426690002</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.297004062321434</v>
+        <v>-4.632974612966457</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.743755295583873</v>
+        <v>1.807726157189672</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.2488957400449104</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.810609870716949</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.673142915745416</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.549479216329158</v>
+        <v>-4.885449766974181</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.654635723036197</v>
+        <v>1.718606584641996</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.2488957400449104</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.822480359772363</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.67435345026436</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.84237497280857</v>
+        <v>-5.178345523453594</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.538687954963376</v>
+        <v>1.602658816569175</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.2488957400449104</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.823690894291306</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.678475192491681</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.029039100943378</v>
+        <v>-5.365009651588402</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.468144045936774</v>
+        <v>1.532114907542573</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3884289464076534</v>
+        <v>0.2221567692203505</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.811769254023892</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.673553045227871</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.17505978785734</v>
+        <v>-5.511030338502364</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.404813623907379</v>
+        <v>1.468784485513178</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.2130736774264936</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.801397251683767</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.835757101926915</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.266773796966925</v>
+        <v>-5.602744347611949</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.530332076962589</v>
+        <v>1.594302938568388</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.2130736774264936</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.963601308382811</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.830603739890729</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.298425456026894</v>
+        <v>-5.634396006671918</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.512518051302415</v>
+        <v>1.576488912908214</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3741773973693562</v>
+        <v>0.2079052201820534</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.955346871999962</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.84083315745922</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.367491510599831</v>
+        <v>-5.703462061244855</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.495121047041732</v>
+        <v>1.559091908647531</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3118065198757461</v>
+        <v>0.1455343426884433</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.928153763072286</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.849758795915123</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.469467632848239</v>
+        <v>-5.805438183493262</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.463256236598271</v>
+        <v>1.52722709820407</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2098303976273386</v>
+        <v>0.04355822044003577</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.875893728179145</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.841911683159298</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.359461349371017</v>
+        <v>-5.69543190001604</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.499411637233335</v>
+        <v>1.563382498839134</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2330349695446138</v>
+        <v>0.06676279235731097</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.881969358573685</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.846161693881272</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.216401773630091</v>
+        <v>-5.552372324275114</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.56088547825168</v>
+        <v>1.624856339857479</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2410483961345931</v>
+        <v>0.07477621894729025</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.891027425249647</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.853422576763808</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.914955048158253</v>
+        <v>-5.250925598803277</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.688725051322951</v>
+        <v>1.75269591292875</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.3762229444191275</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>4.079156343415285</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.854393754516519</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.939545292393437</v>
+        <v>-5.275515843038461</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.679860131381588</v>
+        <v>1.743830992987387</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.3762229444191275</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>4.080127521167996</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.855236658896275</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.888506916386917</v>
+        <v>-5.22447746703194</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.701118386163952</v>
+        <v>1.765089247769751</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.3762229444191275</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>4.080970425547751</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.87427475777042</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.847367621520286</v>
+        <v>-5.18333817216531</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.736612202984749</v>
+        <v>1.800583064590549</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5836344164730611</v>
+        <v>0.4173622392857583</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>4.124692101341875</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.690458753894355</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.750732709501646</v>
+        <v>-5.08670326014667</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.59145016391614</v>
+        <v>1.655421025521939</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6802693284917011</v>
+        <v>0.5139971513043983</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.998857044676994</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.693960797968319</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.681694698553178</v>
+        <v>-5.017665249198202</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.622567412369491</v>
+        <v>1.686538273975291</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7493073394401691</v>
+        <v>0.5830351622528663</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>4.043781895320039</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.678387617044401</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.517198364362216</v>
+        <v>-4.85316891500724</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.672792765121959</v>
+        <v>1.736763626727758</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.913803673631131</v>
+        <v>0.7475314964438282</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>4.126906514910698</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.677575327480831</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.440099762820344</v>
+        <v>-4.776070313465367</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.702819916175137</v>
+        <v>1.766790777780936</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.913803673631131</v>
+        <v>0.7475314964438282</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>4.126094225347128</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.687444106605903</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.450484957710233</v>
+        <v>-4.786455508355257</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.708534617344254</v>
+        <v>1.772505478950053</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9034184787412417</v>
+        <v>0.7371463015539389</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>4.129731887538267</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.758281112382329</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.469073116432458</v>
+        <v>-4.805043667077482</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.771936359631789</v>
+        <v>1.835907221237588</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8848303200190164</v>
+        <v>0.7185581428317136</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>4.189415998081357</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.755150123200627</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.469371663128494</v>
+        <v>-4.805342213773518</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.768685951771673</v>
+        <v>1.832656813377472</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8845317733229805</v>
+        <v>0.7182595961356777</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>4.186105880882034</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.759681018140018</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.368548529438066</v>
+        <v>-4.70451908008309</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.813546100187236</v>
+        <v>1.877516961793035</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8969959888073343</v>
+        <v>0.7307238116200315</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>4.198115305112037</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.759810271618562</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.177767168685659</v>
+        <v>-4.513737719330682</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.889987897966742</v>
+        <v>1.953958759572541</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.087777349559742</v>
+        <v>0.9215051723724389</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.312713375042025</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.739647117356158</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.070803810836237</v>
+        <v>-4.40677436148126</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.912610086844107</v>
+        <v>1.976580948449906</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>0.9799697803322404</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.327628985555503</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.774614053968217</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.015473222934475</v>
+        <v>-4.351443773579498</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.969709258616871</v>
+        <v>2.03368012022267</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.035300368234003</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.395794274908618</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.768300621869654</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.003419096021512</v>
+        <v>-4.339389646666535</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.968217477283494</v>
+        <v>2.032188338889293</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.047354495146965</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.396713318957834</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.77018125205379</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.044574215589733</v>
+        <v>-4.380544766234756</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.953636059640341</v>
+        <v>2.01760692124614</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.006199375578744</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.373900877401037</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.783032277931673</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.976525652898203</v>
+        <v>-4.312496203543226</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.993706510594835</v>
+        <v>2.057677372200635</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.074247938270274</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.427581040893838</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013425</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.803234948105267</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.208126046067703</v>
+        <v>-4.544096596712727</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.92126902350063</v>
+        <v>1.985239885106429</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.074247938270274</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.447783711067432</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.66674720149897</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.786841184172149</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.258177591596922</v>
+        <v>-4.594148142241946</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.884854641355824</v>
+        <v>1.948825502961623</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.074247938270274</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.431389947134313</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.747093097765616</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.433284424173367</v>
+        <v>-4.769254974818391</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.775063821918713</v>
+        <v>1.839034683524512</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.074247938270274</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.391641860727781</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.754115716762556</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.237184270742844</v>
+        <v>-4.573154821387868</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.860526502287862</v>
+        <v>1.924497363893661</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.270348091700797</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.516324571783034</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.85328671633546</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.08415887862956</v>
+        <v>-4.420129429274583</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.02090765870608</v>
+        <v>2.084878520311879</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.423373483814081</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.707310806623909</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>4.040752941243753</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.11246619250283</v>
+        <v>-4.448436743147854</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.197050958065065</v>
+        <v>2.261021819670864</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.423373483814081</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.894777031532201</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>4.010155892597835</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.279059417616352</v>
+        <v>-4.615029968261376</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.099816619373738</v>
+        <v>2.163787480979537</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.256780258700559</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.76422404781817</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>4.013832295259553</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.256023624254786</v>
+        <v>-4.59199417489981</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.112707339380083</v>
+        <v>2.176678200985881</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.256780258700559</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.767900450479888</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>4.011450350383048</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.22677764379909</v>
+        <v>-4.562748194444113</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.122023786685856</v>
+        <v>2.185994648291655</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.256780258700559</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.765518505603383</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>4.008743589540683</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.333703191676941</v>
+        <v>-4.669673742321964</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.076546806692351</v>
+        <v>2.140517668298149</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.149854710822707</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.698656416034307</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>4.010172391683917</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.47872175018419</v>
+        <v>-4.814692300829213</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.019968185432686</v>
+        <v>2.083939047038484</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.004836152315459</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.613074083073193</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>4.11010363094167</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.597063515968907</v>
+        <v>-4.933034066613931</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.072562718376552</v>
+        <v>2.13653357998235</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.015522190878349</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.71941694546868</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>4.107889328067609</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.648473938289615</v>
+        <v>-4.984444488934638</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.049784246574208</v>
+        <v>2.113755108180006</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.015522190878349</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.717202642594619</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437327</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>4.107792456141898</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.727893389497367</v>
+        <v>-5.06386394014239</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.017919594165396</v>
+        <v>2.081890455771195</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.015522190878349</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.717105770668908</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>4.107786349699942</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.823356387414584</v>
+        <v>-5.159326938059608</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.979728288556552</v>
+        <v>2.043699150162351</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.015522190878349</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.717099664226952</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>4.105882746262552</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.758980476563869</v>
+        <v>-5.094951027208893</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.003575049459449</v>
+        <v>2.067545911065248</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.079898101729064</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.753821607299991</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>4.111616564010279</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.814349638696063</v>
+        <v>-5.150320189341087</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.987161202354298</v>
+        <v>2.051132063960097</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.079898101729064</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.759555425047718</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>4.111154927353212</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.832568105693672</v>
+        <v>-5.168538656338695</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.979412178898187</v>
+        <v>2.043383040503986</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>1.054791664473222</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.744029926037145</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>4.131029320203531</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.744361271546094</v>
+        <v>-5.080331822191117</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.034569305407537</v>
+        <v>2.098540167013337</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>1.054791664473222</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.763904318887464</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>4.114730020728259</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.638326276340784</v>
+        <v>-4.974296826985808</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.060684004014388</v>
+        <v>2.124654865620188</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>1.054791664473222</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.747605019412193</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>4.117160970192304</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.455114613207689</v>
+        <v>-4.791085163852713</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.136399618731672</v>
+        <v>2.200370480337472</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>1.054791664473222</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.750035968876238</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.901746294407872</v>
+        <v>4.100105376271681</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.383393166193838</v>
+        <v>-4.719363716838862</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.148032603616589</v>
+        <v>2.212003465222389</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>1.126513111487073</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.677417467612498</v>
+        <v>4.776013243163925</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.848662040329044</v>
+        <v>4.047021122192853</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.361020140586132</v>
+        <v>-4.696990691231155</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.103897559780843</v>
+        <v>2.167868421386643</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>1.137768862599974</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.63108666420141</v>
+        <v>4.729682439752838</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.0338602452144</v>
+        <v>4.232219327078209</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.394036436496877</v>
+        <v>-4.7300069871419</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.275889246301901</v>
+        <v>2.339860107907701</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>1.068331485933222</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.774622443086715</v>
+        <v>4.873218218638143</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.025781471042649</v>
+        <v>4.224140552906458</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.382508800847268</v>
+        <v>-4.718479351492292</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.272421526389993</v>
+        <v>2.336392387995794</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>1.127332144134585</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.801944063835782</v>
+        <v>4.900539839387209</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029449583564437</v>
+        <v>4.227808665428246</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.479850302189637</v>
+        <v>-4.81582085283466</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.237153038374835</v>
+        <v>2.301123899980634</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>1.082911961969097</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.778960067058277</v>
+        <v>4.877555842609705</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.030700665757275</v>
+        <v>4.229059747621084</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.565706331529603</v>
+        <v>-4.901676882174627</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.204061708831686</v>
+        <v>2.268032570437486</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>1.040535892742962</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.754785507715434</v>
+        <v>4.853381283266861</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>4.211478949441586</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.574543128945723</v>
+        <v>-4.910513679590746</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.18294619168574</v>
+        <v>2.24691705329154</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>1.033093720101611</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.732739405951126</v>
+        <v>4.831335181502553</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>4.221643460486636</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.665925691511181</v>
+        <v>-4.998905424654369</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.156557677704606</v>
+        <v>2.22172486631114</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>0.9698817515864826</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.720964986164568</v>
+        <v>4.803572511438525</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.323771718310903</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.654218973524175</v>
+        <v>-4.987198706667363</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.263368622723677</v>
+        <v>2.32853581133021</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>0.981588469573489</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.83011727478104</v>
+        <v>4.912724800054996</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.326804057042308</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.725131047266453</v>
+        <v>-5.058110780409641</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.238036131958171</v>
+        <v>2.303203320564704</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.174507730556575</v>
+        <v>0.981588469573489</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.833149613512445</v>
+        <v>4.915757138786401</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.539708890320366</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.735447145432805</v>
+        <v>-5.068426878575993</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.446814525969688</v>
+        <v>2.511981714576221</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.174507730556575</v>
+        <v>0.981588469573489</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.046054446790503</v>
+        <v>5.128661972064459</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.538887557232456</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.735353177415432</v>
+        <v>-5.06833291055862</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.446030780088726</v>
+        <v>2.51119796869526</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.045455030510984</v>
+        <v>5.12806255578494</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.533119543176809</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.883719405071577</v>
+        <v>-5.216699138214765</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.380916274970622</v>
+        <v>2.446083463577156</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.039687016455337</v>
+        <v>5.122294541729294</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.533119543176809</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.882770981953539</v>
+        <v>-5.215750715096727</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.381295644217838</v>
+        <v>2.446462832824371</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.039687016455337</v>
+        <v>5.122294541729294</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.545847151157902</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.98304079991256</v>
+        <v>-5.316020533055748</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.353915325015321</v>
+        <v>2.419082513621855</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.052414624436429</v>
+        <v>5.135022149710386</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.547793149582289</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.977048553123748</v>
+        <v>-5.310028286266936</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.358258222155234</v>
+        <v>2.423425410761767</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.054360622860817</v>
+        <v>5.136968148134773</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.541447285600058</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.888490591992981</v>
+        <v>-5.221470325136169</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.387335542625309</v>
+        <v>2.452502731231843</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.048014758878586</v>
+        <v>5.130622284152542</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.540755963039054</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.870731514489907</v>
+        <v>-5.203711247633095</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.393747851065535</v>
+        <v>2.458915039672068</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.174877591903893</v>
+        <v>0.981958330920807</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.047323436317582</v>
+        <v>5.129930961591538</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.553538148947641</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.726194172308852</v>
+        <v>-5.104081096584027</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.464344973846543</v>
+        <v>2.511549286000282</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.319414934084948</v>
+        <v>1.081588481969874</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.146828027534801</v>
+        <v>5.202491238129565</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.742692414446367</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.775593680997863</v>
+        <v>-5.153480605273038</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.633739435869666</v>
+        <v>2.680943748023404</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.329673767516693</v>
+        <v>1.091847315401619</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.342137593092574</v>
+        <v>5.397800803687339</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.729881087549229</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.568909207355487</v>
+        <v>-4.946796131630662</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.703601898429478</v>
+        <v>2.750806210583217</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.536358241159068</v>
+        <v>1.298531789043995</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.453336950380862</v>
+        <v>5.509000160975626</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.731882601203334</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.603066102353013</v>
+        <v>-4.980953026628188</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.691940654084573</v>
+        <v>2.739144966238311</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.452774471618256</v>
+        <v>1.214948019503182</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.405188202310479</v>
+        <v>5.460851412905243</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>5.085379715193001</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.510476623291557</v>
+        <v>-4.888363547566732</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.082473559698823</v>
+        <v>3.129677871852561</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.452774471618256</v>
+        <v>1.214948019503182</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.758685316300147</v>
+        <v>5.814348526894911</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>5.089942826760105</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.570365251115107</v>
+        <v>-4.948252175390282</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.063081220136506</v>
+        <v>3.110285532290244</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.438652556930791</v>
+        <v>1.200826104815718</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.754775279054772</v>
+        <v>5.810438489649536</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>5.139772768083632</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.518148941318765</v>
+        <v>-4.89603586559394</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.13379768537857</v>
+        <v>3.181001997532309</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.438652556930791</v>
+        <v>1.200826104815718</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.804605220378299</v>
+        <v>5.860268430973063</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>5.148586738293643</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.48625142423352</v>
+        <v>-4.864138348508694</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.155370662422679</v>
+        <v>3.202574974576418</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.470550074016037</v>
+        <v>1.232723621900963</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.832557700839457</v>
+        <v>5.888220911434221</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>5.14422432233284</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.50100674843366</v>
+        <v>-4.878893672708835</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.14510611678182</v>
+        <v>3.192310428935558</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.470550074016037</v>
+        <v>1.232723621900963</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.828195284878654</v>
+        <v>5.883858495473418</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>5.13514882574912</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.451542125063749</v>
+        <v>-4.829429049338923</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.155816469546064</v>
+        <v>3.203020781699803</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.520014697385949</v>
+        <v>1.282188245270875</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.848798562316881</v>
+        <v>5.904461772911645</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>5.131556493464054</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.288434132910133</v>
+        <v>-4.666321057185308</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.217467334122445</v>
+        <v>3.264671646276184</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.683122689539564</v>
+        <v>1.44529623742449</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.943071025323984</v>
+        <v>5.998734235918748</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>5.140603530155182</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.155626507412967</v>
+        <v>-4.533513431688141</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.27963742101244</v>
+        <v>3.326841733166178</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.683122689539564</v>
+        <v>1.44529623742449</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.952118062015113</v>
+        <v>6.007781272609876</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>5.141460995141304</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.218334423887525</v>
+        <v>-4.596221348162699</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.255411719408738</v>
+        <v>3.302616031562477</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.620414773065006</v>
+        <v>1.382588320949933</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.915350777116499</v>
+        <v>5.971013987711264</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578998</v>
+        <v>3.928304320797588</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>5.104370411931656</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.170326300043832</v>
+        <v>-4.548213224319007</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.237524385736568</v>
+        <v>3.284728697890306</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.620414773065006</v>
+        <v>1.382588320949933</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.878260193906852</v>
+        <v>5.933923404501616</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.899435465751616</v>
+        <v>3.835062122073374</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>5.108302665489607</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.204408565301208</v>
+        <v>-4.560153845362353</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.227823733191567</v>
+        <v>3.283884703030918</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.586332507807629</v>
+        <v>1.370647699906586</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.861743088310376</v>
+        <v>5.930691285433559</v>
       </c>
     </row>
   </sheetData>
